--- a/tests/optim_results.xlsx
+++ b/tests/optim_results.xlsx
@@ -10,13 +10,14 @@
     <sheet name="Version" sheetId="1" r:id="rId1"/>
     <sheet name="Outcomes" sheetId="2" r:id="rId2"/>
     <sheet name="Budget &amp; coverage" sheetId="3" r:id="rId3"/>
+    <sheet name="Economic costs" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="69">
   <si>
     <t>Version</t>
   </si>
@@ -27,7 +28,7 @@
     <t>2.0.11</t>
   </si>
   <si>
-    <t>2025-04-03</t>
+    <t>2025-06-02</t>
   </si>
   <si>
     <t>Scenario</t>
@@ -220,6 +221,9 @@
   </si>
   <si>
     <t>Excess budget not allocated</t>
+  </si>
+  <si>
+    <t>Total (discounted)</t>
   </si>
 </sst>
 </file>
@@ -2583,46 +2587,46 @@
         <v>0</v>
       </c>
       <c r="E38" s="3">
-        <v>1175832.123579968</v>
+        <v>1175832.3197034</v>
       </c>
       <c r="F38" s="3">
-        <v>1182743.764993791</v>
+        <v>1182743.583599751</v>
       </c>
       <c r="G38" s="3">
-        <v>1191948.40819077</v>
+        <v>1191947.195543737</v>
       </c>
       <c r="H38" s="3">
-        <v>1203119.925619593</v>
+        <v>1203117.36944141</v>
       </c>
       <c r="I38" s="3">
-        <v>1216741.571443237</v>
+        <v>1216737.758956869</v>
       </c>
       <c r="J38" s="3">
-        <v>1232680.179020679</v>
+        <v>1232675.355910402</v>
       </c>
       <c r="K38" s="3">
-        <v>1250934.4234203</v>
+        <v>1250928.838441119</v>
       </c>
       <c r="L38" s="3">
-        <v>1270974.844009404</v>
+        <v>1270968.703921536</v>
       </c>
       <c r="M38" s="3">
-        <v>1292390.496526008</v>
+        <v>1292383.958059205</v>
       </c>
       <c r="N38" s="3">
-        <v>1315370.988433532</v>
+        <v>1315364.164187306</v>
       </c>
       <c r="O38" s="3">
-        <v>1339488.231608682</v>
+        <v>1339481.204829059</v>
       </c>
       <c r="P38" s="3">
-        <v>1364296.025483156</v>
+        <v>1364288.856947432</v>
       </c>
       <c r="Q38" s="3">
-        <v>1389798.796363981</v>
+        <v>1389791.527737485</v>
       </c>
       <c r="R38" s="3">
-        <v>16426319.7786931</v>
+        <v>16426260.83727871</v>
       </c>
     </row>
     <row r="39" spans="1:18">
@@ -2637,46 +2641,46 @@
         <v>0</v>
       </c>
       <c r="E39" s="3">
-        <v>193686.0812734824</v>
+        <v>193686.1177349009</v>
       </c>
       <c r="F39" s="3">
-        <v>184369.180786266</v>
+        <v>184373.1754668536</v>
       </c>
       <c r="G39" s="3">
-        <v>187446.1163184602</v>
+        <v>187450.1030931</v>
       </c>
       <c r="H39" s="3">
-        <v>190821.5805548496</v>
+        <v>190825.5428937082</v>
       </c>
       <c r="I39" s="3">
-        <v>194734.8072265953</v>
+        <v>194738.7795890826</v>
       </c>
       <c r="J39" s="3">
-        <v>198922.6114335892</v>
+        <v>198926.5950014951</v>
       </c>
       <c r="K39" s="3">
-        <v>202871.6259860603</v>
+        <v>202875.5889947208</v>
       </c>
       <c r="L39" s="3">
-        <v>207746.0219057218</v>
+        <v>207749.9935157691</v>
       </c>
       <c r="M39" s="3">
-        <v>212363.7671780836</v>
+        <v>212367.7519186857</v>
       </c>
       <c r="N39" s="3">
-        <v>217147.7740770171</v>
+        <v>217151.738625448</v>
       </c>
       <c r="O39" s="3">
-        <v>221872.147365741</v>
+        <v>221876.108469988</v>
       </c>
       <c r="P39" s="3">
-        <v>227116.415251906</v>
+        <v>227120.3866010258</v>
       </c>
       <c r="Q39" s="3">
-        <v>232039.7969106874</v>
+        <v>232043.7662293537</v>
       </c>
       <c r="R39" s="3">
-        <v>2671137.92626846</v>
+        <v>2671185.648134131</v>
       </c>
     </row>
     <row r="40" spans="1:18">
@@ -2691,46 +2695,46 @@
         <v>0</v>
       </c>
       <c r="E40" s="3">
-        <v>760857.6789735613</v>
+        <v>760857.4842483696</v>
       </c>
       <c r="F40" s="3">
-        <v>762837.678441604</v>
+        <v>762837.8475193604</v>
       </c>
       <c r="G40" s="3">
-        <v>764076.9158105713</v>
+        <v>764077.8624219405</v>
       </c>
       <c r="H40" s="3">
-        <v>766575.9931942485</v>
+        <v>766577.6661240663</v>
       </c>
       <c r="I40" s="3">
-        <v>771745.0873058606</v>
+        <v>771747.3086573835</v>
       </c>
       <c r="J40" s="3">
-        <v>779680.3501268849</v>
+        <v>779682.9658912326</v>
       </c>
       <c r="K40" s="3">
-        <v>790231.2064151339</v>
+        <v>790234.1020524884</v>
       </c>
       <c r="L40" s="3">
-        <v>802818.1400502989</v>
+        <v>802821.2316049825</v>
       </c>
       <c r="M40" s="3">
-        <v>816976.0967942742</v>
+        <v>816979.3259898393</v>
       </c>
       <c r="N40" s="3">
-        <v>832671.7194784554</v>
+        <v>832675.0457168444</v>
       </c>
       <c r="O40" s="3">
-        <v>849500.7071164002</v>
+        <v>849504.1000582401</v>
       </c>
       <c r="P40" s="3">
-        <v>867065.6365297214</v>
+        <v>867069.0754072068</v>
       </c>
       <c r="Q40" s="3">
-        <v>885305.3943691883</v>
+        <v>885308.8655897153</v>
       </c>
       <c r="R40" s="3">
-        <v>10450342.6046062</v>
+        <v>10450372.88128167</v>
       </c>
     </row>
     <row r="41" spans="1:18">
@@ -2745,46 +2749,46 @@
         <v>0</v>
       </c>
       <c r="E41" s="3">
-        <v>57321.78934274425</v>
+        <v>57321.76811400868</v>
       </c>
       <c r="F41" s="3">
-        <v>57598.3309542033</v>
+        <v>57598.30930885871</v>
       </c>
       <c r="G41" s="3">
-        <v>57920.00646346527</v>
+        <v>57919.97660046934</v>
       </c>
       <c r="H41" s="3">
-        <v>58345.9482132451</v>
+        <v>58345.89908722441</v>
       </c>
       <c r="I41" s="3">
-        <v>58929.84033328133</v>
+        <v>58929.76939936465</v>
       </c>
       <c r="J41" s="3">
-        <v>59670.42510189768</v>
+        <v>59670.33525597511</v>
       </c>
       <c r="K41" s="3">
-        <v>60562.87033687354</v>
+        <v>60562.76570623495</v>
       </c>
       <c r="L41" s="3">
-        <v>61571.71166907372</v>
+        <v>61571.59600327067</v>
       </c>
       <c r="M41" s="3">
-        <v>62671.55102692793</v>
+        <v>62671.42733639605</v>
       </c>
       <c r="N41" s="3">
-        <v>63866.95752481906</v>
+        <v>63866.82800437111</v>
       </c>
       <c r="O41" s="3">
-        <v>65131.53921335738</v>
+        <v>65131.40547352287</v>
       </c>
       <c r="P41" s="3">
-        <v>66439.61935905306</v>
+        <v>66439.48261945235</v>
       </c>
       <c r="Q41" s="3">
-        <v>67790.38487448612</v>
+        <v>67790.2459959049</v>
       </c>
       <c r="R41" s="3">
-        <v>797820.9744134278</v>
+        <v>797819.8089050538</v>
       </c>
     </row>
     <row r="42" spans="1:18">
@@ -2799,46 +2803,46 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>405972.8994525467</v>
+        <v>405972.4607173959</v>
       </c>
       <c r="F42" s="3">
-        <v>407836.9609813858</v>
+        <v>407836.5197581442</v>
       </c>
       <c r="G42" s="3">
-        <v>410026.3954173027</v>
+        <v>410025.9008889984</v>
       </c>
       <c r="H42" s="3">
-        <v>412892.3365020325</v>
+        <v>412891.7133094617</v>
       </c>
       <c r="I42" s="3">
-        <v>416831.657726891</v>
+        <v>416830.8868519537</v>
       </c>
       <c r="J42" s="3">
-        <v>421836.5977387279</v>
+        <v>421835.6983660189</v>
       </c>
       <c r="K42" s="3">
-        <v>427875.3103395909</v>
+        <v>427874.3105431545</v>
       </c>
       <c r="L42" s="3">
-        <v>434715.2945139665</v>
+        <v>434714.2197526995</v>
       </c>
       <c r="M42" s="3">
-        <v>442172.9285948603</v>
+        <v>442171.7995152021</v>
       </c>
       <c r="N42" s="3">
-        <v>450280.9652932548</v>
+        <v>450279.7969501314</v>
       </c>
       <c r="O42" s="3">
-        <v>458864.8942771974</v>
+        <v>458863.6975970746</v>
       </c>
       <c r="P42" s="3">
-        <v>467747.8640537847</v>
+        <v>467746.6473241197</v>
       </c>
       <c r="Q42" s="3">
-        <v>476918.0031586071</v>
+        <v>476916.7723315147</v>
       </c>
       <c r="R42" s="3">
-        <v>5633972.108050149</v>
+        <v>5633960.423905869</v>
       </c>
     </row>
     <row r="43" spans="1:18">
@@ -2853,46 +2857,46 @@
         <v>0</v>
       </c>
       <c r="E43" s="3">
-        <v>1530716.903100983</v>
+        <v>1530717.343234374</v>
       </c>
       <c r="F43" s="3">
-        <v>1537744.482454009</v>
+        <v>1537744.911360967</v>
       </c>
       <c r="G43" s="3">
-        <v>1545998.928584039</v>
+        <v>1545999.15707668</v>
       </c>
       <c r="H43" s="3">
-        <v>1556803.582311809</v>
+        <v>1556803.322256015</v>
       </c>
       <c r="I43" s="3">
-        <v>1571655.001022207</v>
+        <v>1571654.180762299</v>
       </c>
       <c r="J43" s="3">
-        <v>1590523.931408836</v>
+        <v>1590522.623435616</v>
       </c>
       <c r="K43" s="3">
-        <v>1613290.319495843</v>
+        <v>1613288.629950453</v>
       </c>
       <c r="L43" s="3">
-        <v>1639077.689545736</v>
+        <v>1639075.715773819</v>
       </c>
       <c r="M43" s="3">
-        <v>1667193.664725422</v>
+        <v>1667191.484533842</v>
       </c>
       <c r="N43" s="3">
-        <v>1697761.742618732</v>
+        <v>1697759.412954019</v>
       </c>
       <c r="O43" s="3">
-        <v>1730124.044447885</v>
+        <v>1730121.607290225</v>
       </c>
       <c r="P43" s="3">
-        <v>1763613.797959093</v>
+        <v>1763611.285030519</v>
       </c>
       <c r="Q43" s="3">
-        <v>1798186.187574563</v>
+        <v>1798183.620995685</v>
       </c>
       <c r="R43" s="3">
-        <v>21242690.27524915</v>
+        <v>21242673.29465451</v>
       </c>
     </row>
     <row r="44" spans="1:18">
@@ -2907,46 +2911,46 @@
         <v>0</v>
       </c>
       <c r="E44" s="3">
-        <v>1879368.013210785</v>
+        <v>1879368.035837761</v>
       </c>
       <c r="F44" s="3">
-        <v>1887983.112481192</v>
+        <v>1887983.121810253</v>
       </c>
       <c r="G44" s="3">
-        <v>1898105.317537876</v>
+        <v>1898105.081365209</v>
       </c>
       <c r="H44" s="3">
-        <v>1911349.970600596</v>
+        <v>1911349.136478252</v>
       </c>
       <c r="I44" s="3">
-        <v>1929556.818415816</v>
+        <v>1929555.298214888</v>
       </c>
       <c r="J44" s="3">
-        <v>1952690.104045666</v>
+        <v>1952687.98654566</v>
       </c>
       <c r="K44" s="3">
-        <v>1980602.759498561</v>
+        <v>1980600.174787372</v>
       </c>
       <c r="L44" s="3">
-        <v>2012221.272390629</v>
+        <v>2012218.339523248</v>
       </c>
       <c r="M44" s="3">
-        <v>2046695.042293354</v>
+        <v>2046691.856712648</v>
       </c>
       <c r="N44" s="3">
-        <v>2084175.750387168</v>
+        <v>2084172.381899779</v>
       </c>
       <c r="O44" s="3">
-        <v>2123857.399511725</v>
+        <v>2123853.899413777</v>
       </c>
       <c r="P44" s="3">
-        <v>2164922.042653825</v>
+        <v>2164918.449735186</v>
       </c>
       <c r="Q44" s="3">
-        <v>2207313.805858684</v>
+        <v>2207310.147331295</v>
       </c>
       <c r="R44" s="3">
-        <v>26078841.40888588</v>
+        <v>26078813.90965533</v>
       </c>
     </row>
     <row r="45" spans="1:18">
@@ -2961,46 +2965,46 @@
         <v>0</v>
       </c>
       <c r="E45" s="3">
-        <v>901844.9922978551</v>
+        <v>901845.4115884702</v>
       </c>
       <c r="F45" s="3">
-        <v>907139.586022306</v>
+        <v>907139.7158833216</v>
       </c>
       <c r="G45" s="3">
-        <v>914193.2411919471</v>
+        <v>914192.5811641688</v>
       </c>
       <c r="H45" s="3">
-        <v>922751.1302711973</v>
+        <v>922749.440494883</v>
       </c>
       <c r="I45" s="3">
-        <v>933185.0523678451</v>
+        <v>933182.3995384467</v>
       </c>
       <c r="J45" s="3">
-        <v>945392.962928439</v>
+        <v>945389.5352452748</v>
       </c>
       <c r="K45" s="3">
-        <v>959374.0290083336</v>
+        <v>959370.0170769317</v>
       </c>
       <c r="L45" s="3">
-        <v>974723.4799324072</v>
+        <v>974719.0423321726</v>
       </c>
       <c r="M45" s="3">
-        <v>991125.882044106</v>
+        <v>991121.1388473647</v>
       </c>
       <c r="N45" s="3">
-        <v>1008726.700808479</v>
+        <v>1008721.73830641</v>
       </c>
       <c r="O45" s="3">
-        <v>1027198.470379153</v>
+        <v>1027193.352449694</v>
       </c>
       <c r="P45" s="3">
-        <v>1046199.31225467</v>
+        <v>1046194.085523793</v>
       </c>
       <c r="Q45" s="3">
-        <v>1065732.199243172</v>
+        <v>1065726.895592862</v>
       </c>
       <c r="R45" s="3">
-        <v>12597587.03874991</v>
+        <v>12597545.35404379</v>
       </c>
     </row>
     <row r="46" spans="1:18">
@@ -3015,43 +3019,43 @@
         <v>0.3411657413950535</v>
       </c>
       <c r="E46" s="3">
-        <v>0.3388232137868187</v>
+        <v>0.3388241718842684</v>
       </c>
       <c r="F46" s="3">
-        <v>0.3364048673792279</v>
+        <v>0.3364065266702311</v>
       </c>
       <c r="G46" s="3">
-        <v>0.3347294503037683</v>
+        <v>0.3347315437411663</v>
       </c>
       <c r="H46" s="3">
-        <v>0.3336854048656157</v>
+        <v>0.3336877813516808</v>
       </c>
       <c r="I46" s="3">
-        <v>0.332981446659256</v>
+        <v>0.3329840073074358</v>
       </c>
       <c r="J46" s="3">
-        <v>0.3326556870657815</v>
+        <v>0.3326583571377129</v>
       </c>
       <c r="K46" s="3">
-        <v>0.3327520487021187</v>
+        <v>0.3327547750565599</v>
       </c>
       <c r="L46" s="3">
-        <v>0.332785454576468</v>
+        <v>0.3327882082935035</v>
       </c>
       <c r="M46" s="3">
-        <v>0.3330972346676867</v>
+        <v>0.3330999853955042</v>
       </c>
       <c r="N46" s="3">
-        <v>0.3335353920092599</v>
+        <v>0.3335381240959417</v>
       </c>
       <c r="O46" s="3">
-        <v>0.3340368403603879</v>
+        <v>0.3340395437645804</v>
       </c>
       <c r="P46" s="3">
-        <v>0.3344617740196774</v>
+        <v>0.3344644431900666</v>
       </c>
       <c r="Q46" s="3">
-        <v>0.3350425365849719</v>
+        <v>0.3350451634105155</v>
       </c>
       <c r="R46" s="3" t="s">
         <v>19</v>
@@ -3069,43 +3073,43 @@
         <v>0.04535037632743646</v>
       </c>
       <c r="E47" s="3">
-        <v>0.04488112609900785</v>
+        <v>0.04488118074480409</v>
       </c>
       <c r="F47" s="3">
-        <v>0.04498873259907012</v>
+        <v>0.0449887760766396</v>
       </c>
       <c r="G47" s="3">
-        <v>0.04510605256415652</v>
+        <v>0.04510609413317773</v>
       </c>
       <c r="H47" s="3">
-        <v>0.04520584277890138</v>
+        <v>0.04520588577371571</v>
       </c>
       <c r="I47" s="3">
-        <v>0.04531369499634577</v>
+        <v>0.04531374000803324</v>
       </c>
       <c r="J47" s="3">
-        <v>0.04540869468869346</v>
+        <v>0.04540874097489966</v>
       </c>
       <c r="K47" s="3">
-        <v>0.04545813364223705</v>
+        <v>0.04545818048495702</v>
       </c>
       <c r="L47" s="3">
-        <v>0.04554027206161611</v>
+        <v>0.0455403197152341</v>
       </c>
       <c r="M47" s="3">
-        <v>0.04559674284048705</v>
+        <v>0.0455967901260774</v>
       </c>
       <c r="N47" s="3">
-        <v>0.04563593526612331</v>
+        <v>0.04563598226412482</v>
       </c>
       <c r="O47" s="3">
-        <v>0.04566649026449793</v>
+        <v>0.04566653677815394</v>
       </c>
       <c r="P47" s="3">
-        <v>0.04571618743777561</v>
+        <v>0.04571623352190438</v>
       </c>
       <c r="Q47" s="3">
-        <v>0.04574166960543734</v>
+        <v>0.04574171475985124</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>19</v>
@@ -3123,43 +3127,43 @@
         <v>0.2195512735036556</v>
       </c>
       <c r="E48" s="3">
-        <v>0.2271832611426008</v>
+        <v>0.2271829907396787</v>
       </c>
       <c r="F48" s="3">
-        <v>0.226810994480958</v>
+        <v>0.2268107317530315</v>
       </c>
       <c r="G48" s="3">
-        <v>0.2268149077576077</v>
+        <v>0.2268146301535173</v>
       </c>
       <c r="H48" s="3">
-        <v>0.2268782615707898</v>
+        <v>0.2268779815264488</v>
       </c>
       <c r="I48" s="3">
-        <v>0.2269051539977175</v>
+        <v>0.2269048775286703</v>
       </c>
       <c r="J48" s="3">
-        <v>0.2269581391606064</v>
+        <v>0.2269578680932121</v>
       </c>
       <c r="K48" s="3">
-        <v>0.2270427433143329</v>
+        <v>0.2270424780817416</v>
       </c>
       <c r="L48" s="3">
-        <v>0.2270132504864197</v>
+        <v>0.2270129910697494</v>
       </c>
       <c r="M48" s="3">
-        <v>0.22706639551817</v>
+        <v>0.2270661417044606</v>
       </c>
       <c r="N48" s="3">
-        <v>0.227097449665679</v>
+        <v>0.227097201271585</v>
       </c>
       <c r="O48" s="3">
-        <v>0.2271117797021175</v>
+        <v>0.2271115366076182</v>
       </c>
       <c r="P48" s="3">
-        <v>0.2270883954976517</v>
+        <v>0.2270881574405861</v>
       </c>
       <c r="Q48" s="3">
-        <v>0.2271246874607325</v>
+        <v>0.2271244542706852</v>
       </c>
       <c r="R48" s="3" t="s">
         <v>19</v>
@@ -3177,46 +3181,46 @@
         <v>0</v>
       </c>
       <c r="E49" s="3">
-        <v>7402.800673686026</v>
+        <v>7402.905626281405</v>
       </c>
       <c r="F49" s="3">
-        <v>7554.182018271404</v>
+        <v>7554.286970866782</v>
       </c>
       <c r="G49" s="3">
-        <v>7743.408699003125</v>
+        <v>7743.513651598503</v>
       </c>
       <c r="H49" s="3">
-        <v>7894.7900435885</v>
+        <v>7894.894996183879</v>
       </c>
       <c r="I49" s="3">
-        <v>8046.171388173879</v>
+        <v>8046.276340769256</v>
       </c>
       <c r="J49" s="3">
-        <v>8235.398068905597</v>
+        <v>8235.503021500976</v>
       </c>
       <c r="K49" s="3">
-        <v>8424.62474963732</v>
+        <v>8424.729702232698</v>
       </c>
       <c r="L49" s="3">
-        <v>8576.006094222697</v>
+        <v>8576.111046818074</v>
       </c>
       <c r="M49" s="3">
-        <v>8803.078111100762</v>
+        <v>8803.183063696142</v>
       </c>
       <c r="N49" s="3">
-        <v>8992.304791832481</v>
+        <v>8992.409744427861</v>
       </c>
       <c r="O49" s="3">
-        <v>9181.531472564206</v>
+        <v>9181.636425159584</v>
       </c>
       <c r="P49" s="3">
-        <v>9370.758153295927</v>
+        <v>9370.863105891305</v>
       </c>
       <c r="Q49" s="3">
-        <v>9597.830170173991</v>
+        <v>9597.935122769371</v>
       </c>
       <c r="R49" s="3">
-        <v>109822.8844344559</v>
+        <v>109824.2488181958</v>
       </c>
     </row>
     <row r="50" spans="1:18">
@@ -3231,46 +3235,46 @@
         <v>0</v>
       </c>
       <c r="E50" s="3">
-        <v>358569.1930935011</v>
+        <v>358607.6065074039</v>
       </c>
       <c r="F50" s="3">
-        <v>370967.2078295517</v>
+        <v>371005.783290306</v>
       </c>
       <c r="G50" s="3">
-        <v>382666.969396128</v>
+        <v>382705.3535736059</v>
       </c>
       <c r="H50" s="3">
-        <v>393372.9063008832</v>
+        <v>393411.2782385085</v>
       </c>
       <c r="I50" s="3">
-        <v>405818.1682112502</v>
+        <v>405856.6936838675</v>
       </c>
       <c r="J50" s="3">
-        <v>419214.1392946931</v>
+        <v>419252.6470263903</v>
       </c>
       <c r="K50" s="3">
-        <v>430825.701265519</v>
+        <v>430864.0336036215</v>
       </c>
       <c r="L50" s="3">
-        <v>445111.4369681897</v>
+        <v>445150.0703935732</v>
       </c>
       <c r="M50" s="3">
-        <v>459378.2278633608</v>
+        <v>459416.6866644556</v>
       </c>
       <c r="N50" s="3">
-        <v>472759.1005648815</v>
+        <v>472797.5443451197</v>
       </c>
       <c r="O50" s="3">
-        <v>486136.7416009393</v>
+        <v>486175.1709425243</v>
       </c>
       <c r="P50" s="3">
-        <v>501375.1835530514</v>
+        <v>501413.74234622</v>
       </c>
       <c r="Q50" s="3">
-        <v>515557.0644650897</v>
+        <v>515595.4639310081</v>
       </c>
       <c r="R50" s="3">
-        <v>5641752.040407038</v>
+        <v>5642252.074546603</v>
       </c>
     </row>
     <row r="51" spans="1:18">
@@ -3285,43 +3289,43 @@
         <v>0.18698022</v>
       </c>
       <c r="E51" s="3">
-        <v>0.1418453030494604</v>
+        <v>0.1418604988957326</v>
       </c>
       <c r="F51" s="3">
-        <v>0.1434145735752398</v>
+        <v>0.1434294867080931</v>
       </c>
       <c r="G51" s="3">
-        <v>0.1452959149442141</v>
+        <v>0.1453104891422298</v>
       </c>
       <c r="H51" s="3">
-        <v>0.1467405163525336</v>
+        <v>0.1467548302970133</v>
       </c>
       <c r="I51" s="3">
-        <v>0.1481344299921403</v>
+        <v>0.1481484928147869</v>
       </c>
       <c r="J51" s="3">
-        <v>0.1498095193444572</v>
+        <v>0.1498232803897938</v>
       </c>
       <c r="K51" s="3">
-        <v>0.1514142267912145</v>
+        <v>0.1514276987389601</v>
       </c>
       <c r="L51" s="3">
-        <v>0.1526502493865681</v>
+        <v>0.1526634986574914</v>
       </c>
       <c r="M51" s="3">
-        <v>0.154429523848428</v>
+        <v>0.1544424525724741</v>
       </c>
       <c r="N51" s="3">
-        <v>0.1558477861006351</v>
+        <v>0.155860459316301</v>
       </c>
       <c r="O51" s="3">
-        <v>0.1572110769477179</v>
+        <v>0.1572235045584289</v>
       </c>
       <c r="P51" s="3">
-        <v>0.1585225316409192</v>
+        <v>0.158534722985267</v>
       </c>
       <c r="Q51" s="3">
-        <v>0.1600319233621651</v>
+        <v>0.1600438427806166</v>
       </c>
       <c r="R51" s="3" t="s">
         <v>19</v>
@@ -3339,46 +3343,46 @@
         <v>0</v>
       </c>
       <c r="E52" s="3">
-        <v>2134178.469281729</v>
+        <v>2134163.862428155</v>
       </c>
       <c r="F52" s="3">
-        <v>2214970.503056915</v>
+        <v>2214955.913701895</v>
       </c>
       <c r="G52" s="3">
-        <v>2299165.57392235</v>
+        <v>2299150.981098724</v>
       </c>
       <c r="H52" s="3">
-        <v>2385485.202311963</v>
+        <v>2385470.61574423</v>
       </c>
       <c r="I52" s="3">
-        <v>2470726.54317645</v>
+        <v>2470711.982570886</v>
       </c>
       <c r="J52" s="3">
-        <v>2557650.34937733</v>
+        <v>2557635.797591463</v>
       </c>
       <c r="K52" s="3">
-        <v>2649522.408807549</v>
+        <v>2649507.848021779</v>
       </c>
       <c r="L52" s="3">
-        <v>2740233.789873516</v>
+        <v>2740219.254042136</v>
       </c>
       <c r="M52" s="3">
-        <v>2834807.108169547</v>
+        <v>2834792.569055473</v>
       </c>
       <c r="N52" s="3">
-        <v>2932461.28794332</v>
+        <v>2932446.750257407</v>
       </c>
       <c r="O52" s="3">
-        <v>3032791.013806678</v>
+        <v>3032776.479618701</v>
       </c>
       <c r="P52" s="3">
-        <v>3132857.910862316</v>
+        <v>3132843.393984697</v>
       </c>
       <c r="Q52" s="3">
-        <v>3236625.872320277</v>
+        <v>3236611.354176001</v>
       </c>
       <c r="R52" s="3">
-        <v>34621476.03290994</v>
+        <v>34621286.80229155</v>
       </c>
     </row>
     <row r="53" spans="1:18">
@@ -3393,43 +3397,43 @@
         <v>0.1886948075946863</v>
       </c>
       <c r="E53" s="3">
-        <v>0.1886170291546304</v>
+        <v>0.1886157382123001</v>
       </c>
       <c r="F53" s="3">
-        <v>0.1886355524635235</v>
+        <v>0.18863430997698</v>
       </c>
       <c r="G53" s="3">
-        <v>0.1886416153147034</v>
+        <v>0.1886404180047524</v>
       </c>
       <c r="H53" s="3">
-        <v>0.1886368386084407</v>
+        <v>0.1886356851474925</v>
       </c>
       <c r="I53" s="3">
-        <v>0.1886247384887688</v>
+        <v>0.1886236268763063</v>
       </c>
       <c r="J53" s="3">
-        <v>0.1886083308379116</v>
+        <v>0.188607257748291</v>
       </c>
       <c r="K53" s="3">
-        <v>0.1885931535199888</v>
+        <v>0.1885921170824418</v>
       </c>
       <c r="L53" s="3">
-        <v>0.1885868524892933</v>
+        <v>0.1885858521123552</v>
       </c>
       <c r="M53" s="3">
-        <v>0.1885814989960839</v>
+        <v>0.1885805318022603</v>
       </c>
       <c r="N53" s="3">
-        <v>0.188580268544009</v>
+        <v>0.1885793336567439</v>
       </c>
       <c r="O53" s="3">
-        <v>0.1885791399707505</v>
+        <v>0.1885782362340089</v>
       </c>
       <c r="P53" s="3">
-        <v>0.1885735306477239</v>
+        <v>0.1885726568452903</v>
       </c>
       <c r="Q53" s="3">
-        <v>0.1885580914526415</v>
+        <v>0.1885572456602378</v>
       </c>
       <c r="R53" s="3" t="s">
         <v>19</v>
@@ -3447,46 +3451,46 @@
         <v>0</v>
       </c>
       <c r="E54" s="3">
-        <v>90.08654942952667</v>
+        <v>90.08656638832601</v>
       </c>
       <c r="F54" s="3">
-        <v>86.90925564591915</v>
+        <v>86.91018234523092</v>
       </c>
       <c r="G54" s="3">
-        <v>85.81204527742163</v>
+        <v>85.81326195673059</v>
       </c>
       <c r="H54" s="3">
-        <v>85.26752637351274</v>
+        <v>85.26887702238585</v>
       </c>
       <c r="I54" s="3">
-        <v>84.91587197854048</v>
+        <v>84.91729631943261</v>
       </c>
       <c r="J54" s="3">
-        <v>84.68191293028296</v>
+        <v>84.68338098520917</v>
       </c>
       <c r="K54" s="3">
-        <v>84.55325022370644</v>
+        <v>84.55474392336633</v>
       </c>
       <c r="L54" s="3">
-        <v>84.4479451020035</v>
+        <v>84.44945326242589</v>
       </c>
       <c r="M54" s="3">
-        <v>84.38656795159963</v>
+        <v>84.38808416031965</v>
       </c>
       <c r="N54" s="3">
-        <v>84.3624233463385</v>
+        <v>84.36394179032487</v>
       </c>
       <c r="O54" s="3">
-        <v>84.36238421456393</v>
+        <v>84.36390142272128</v>
       </c>
       <c r="P54" s="3">
-        <v>84.36866583734944</v>
+        <v>84.37017924264191</v>
       </c>
       <c r="Q54" s="3">
-        <v>84.39614301006192</v>
+        <v>84.39765080992517</v>
       </c>
       <c r="R54" s="3">
-        <v>1108.550541320827</v>
+        <v>1108.56751962904</v>
       </c>
     </row>
     <row r="55" spans="1:18">
@@ -3501,43 +3505,43 @@
         <v>0.01226890863757641</v>
       </c>
       <c r="E55" s="3">
-        <v>0.01204884346787182</v>
+        <v>0.01204884930102636</v>
       </c>
       <c r="F55" s="3">
-        <v>0.01210760664494339</v>
+        <v>0.01210760795286879</v>
       </c>
       <c r="G55" s="3">
-        <v>0.01215056814601654</v>
+        <v>0.01215056966301977</v>
       </c>
       <c r="H55" s="3">
-        <v>0.01218303949186056</v>
+        <v>0.0121830419536722</v>
       </c>
       <c r="I55" s="3">
-        <v>0.01221996006024916</v>
+        <v>0.01221996342814459</v>
       </c>
       <c r="J55" s="3">
-        <v>0.01225041491380399</v>
+        <v>0.01225041885547338</v>
       </c>
       <c r="K55" s="3">
-        <v>0.01226191094909547</v>
+        <v>0.01226191522702028</v>
       </c>
       <c r="L55" s="3">
-        <v>0.01229135656160574</v>
+        <v>0.01229136129371825</v>
       </c>
       <c r="M55" s="3">
-        <v>0.01230691708081901</v>
+        <v>0.01230692183846824</v>
       </c>
       <c r="N55" s="3">
-        <v>0.01231698629598657</v>
+        <v>0.01231699115199762</v>
       </c>
       <c r="O55" s="3">
-        <v>0.01232473001826897</v>
+        <v>0.01232473490380169</v>
       </c>
       <c r="P55" s="3">
-        <v>0.01234162859159909</v>
+        <v>0.01234163352983726</v>
       </c>
       <c r="Q55" s="3">
-        <v>0.01234641996098881</v>
+        <v>0.01234642476836554</v>
       </c>
       <c r="R55" s="3" t="s">
         <v>19</v>
@@ -3555,43 +3559,43 @@
         <v>0.03308146768986005</v>
       </c>
       <c r="E56" s="3">
-        <v>0.03283228263113603</v>
+        <v>0.03283233144377772</v>
       </c>
       <c r="F56" s="3">
-        <v>0.03288112595412673</v>
+        <v>0.03288116812377081</v>
       </c>
       <c r="G56" s="3">
-        <v>0.03295548441813998</v>
+        <v>0.03295552447015797</v>
       </c>
       <c r="H56" s="3">
-        <v>0.03302280328704083</v>
+        <v>0.03302284382004352</v>
       </c>
       <c r="I56" s="3">
-        <v>0.03309373493609661</v>
+        <v>0.03309377657988865</v>
       </c>
       <c r="J56" s="3">
-        <v>0.03315827977488947</v>
+        <v>0.03315832211942629</v>
       </c>
       <c r="K56" s="3">
-        <v>0.03319622269314157</v>
+        <v>0.03319626525793674</v>
       </c>
       <c r="L56" s="3">
-        <v>0.03324891550001037</v>
+        <v>0.03324895842151585</v>
       </c>
       <c r="M56" s="3">
-        <v>0.03328982575966805</v>
+        <v>0.03328986828760915</v>
       </c>
       <c r="N56" s="3">
-        <v>0.03331894897013674</v>
+        <v>0.0333189911121272</v>
       </c>
       <c r="O56" s="3">
-        <v>0.03334176024622897</v>
+        <v>0.03334180187435225</v>
       </c>
       <c r="P56" s="3">
-        <v>0.03337455884617652</v>
+        <v>0.03337459999206713</v>
       </c>
       <c r="Q56" s="3">
-        <v>0.03339524964444852</v>
+        <v>0.0333952899914857</v>
       </c>
       <c r="R56" s="3" t="s">
         <v>19</v>
@@ -3609,43 +3613,43 @@
         <v>121000.9090850509</v>
       </c>
       <c r="E57" s="3">
-        <v>119066.9858191897</v>
+        <v>119067.0430064098</v>
       </c>
       <c r="F57" s="3">
-        <v>120495.8153573282</v>
+        <v>120495.7796986048</v>
       </c>
       <c r="G57" s="3">
-        <v>122096.2483016868</v>
+        <v>122096.169488342</v>
       </c>
       <c r="H57" s="3">
-        <v>123878.2000228743</v>
+        <v>123878.0932336232</v>
       </c>
       <c r="I57" s="3">
-        <v>126047.2393812874</v>
+        <v>126047.1128015023</v>
       </c>
       <c r="J57" s="3">
-        <v>128428.2286177628</v>
+        <v>128428.086459891</v>
       </c>
       <c r="K57" s="3">
-        <v>130706.3877452672</v>
+        <v>130706.2340755303</v>
       </c>
       <c r="L57" s="3">
-        <v>133459.619408991</v>
+        <v>133459.4596954238</v>
       </c>
       <c r="M57" s="3">
-        <v>136191.732798852</v>
+        <v>136191.5657732473</v>
       </c>
       <c r="N57" s="3">
-        <v>138948.9673957759</v>
+        <v>138948.7965756768</v>
       </c>
       <c r="O57" s="3">
-        <v>141737.1529342595</v>
+        <v>141736.9793424981</v>
       </c>
       <c r="P57" s="3">
-        <v>144788.8478899129</v>
+        <v>144788.6727496762</v>
       </c>
       <c r="Q57" s="3">
-        <v>147719.9971360329</v>
+        <v>147719.819366999</v>
       </c>
       <c r="R57" s="3" t="s">
         <v>19</v>
@@ -3663,43 +3667,43 @@
         <v>326262.7331074112</v>
       </c>
       <c r="E58" s="3">
-        <v>324449.4744144591</v>
+        <v>324449.9555392381</v>
       </c>
       <c r="F58" s="3">
-        <v>327235.4477558293</v>
+        <v>327235.7352416505</v>
       </c>
       <c r="G58" s="3">
-        <v>331156.614247601</v>
+        <v>331156.7616069776</v>
       </c>
       <c r="H58" s="3">
-        <v>335778.7220209807</v>
+        <v>335778.7768551255</v>
       </c>
       <c r="I58" s="3">
-        <v>341357.4110671838</v>
+        <v>341357.4037370338</v>
       </c>
       <c r="J58" s="3">
-        <v>347617.5431986991</v>
+        <v>347617.4904922499</v>
       </c>
       <c r="K58" s="3">
-        <v>353856.6193329002</v>
+        <v>353856.5335760901</v>
       </c>
       <c r="L58" s="3">
-        <v>361016.9134832572</v>
+        <v>361016.8084993917</v>
       </c>
       <c r="M58" s="3">
-        <v>368394.3773251891</v>
+        <v>368394.253736396</v>
       </c>
       <c r="N58" s="3">
-        <v>375873.8901594456</v>
+        <v>375873.755287621</v>
       </c>
       <c r="O58" s="3">
-        <v>383437.7032285621</v>
+        <v>383437.5603526386</v>
       </c>
       <c r="P58" s="3">
-        <v>391541.8365013273</v>
+        <v>391541.6889279869</v>
       </c>
       <c r="Q58" s="3">
-        <v>399560.860348375</v>
+        <v>399560.7066663301</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>19</v>
@@ -3717,46 +3721,46 @@
         <v>0</v>
       </c>
       <c r="E59" s="3">
-        <v>44786.83034905652</v>
+        <v>44794.42901743967</v>
       </c>
       <c r="F59" s="3">
-        <v>46889.77141746841</v>
+        <v>46897.35740946628</v>
       </c>
       <c r="G59" s="3">
-        <v>48718.55101160111</v>
+        <v>48726.09576439488</v>
       </c>
       <c r="H59" s="3">
-        <v>50347.10175349192</v>
+        <v>50354.64141637526</v>
       </c>
       <c r="I59" s="3">
-        <v>52201.23815016844</v>
+        <v>52208.80533057121</v>
       </c>
       <c r="J59" s="3">
-        <v>54244.01123896913</v>
+        <v>54251.57166503777</v>
       </c>
       <c r="K59" s="3">
-        <v>56051.71019134818</v>
+        <v>56059.23313882243</v>
       </c>
       <c r="L59" s="3">
-        <v>58146.20768098465</v>
+        <v>58153.78746659117</v>
       </c>
       <c r="M59" s="3">
-        <v>60360.93827775291</v>
+        <v>60368.48019609561</v>
       </c>
       <c r="N59" s="3">
-        <v>62394.89330051129</v>
+        <v>62402.42970295395</v>
       </c>
       <c r="O59" s="3">
-        <v>64430.16086712368</v>
+        <v>64437.69185639511</v>
       </c>
       <c r="P59" s="3">
-        <v>66712.56259678728</v>
+        <v>66720.11646373503</v>
       </c>
       <c r="Q59" s="3">
-        <v>68906.92452447336</v>
+        <v>68914.44417534242</v>
       </c>
       <c r="R59" s="3">
-        <v>734190.9013597368</v>
+        <v>734289.0836032208</v>
       </c>
     </row>
     <row r="60" spans="1:18">
@@ -3771,43 +3775,43 @@
         <v>0.5092287374537772</v>
       </c>
       <c r="E60" s="3">
-        <v>0.5124643244076854</v>
+        <v>0.5124657080744158</v>
       </c>
       <c r="F60" s="3">
-        <v>0.5124053968022356</v>
+        <v>0.5124068771335762</v>
       </c>
       <c r="G60" s="3">
-        <v>0.5123873925445415</v>
+        <v>0.5123888645888458</v>
       </c>
       <c r="H60" s="3">
-        <v>0.5123956754599962</v>
+        <v>0.5123971253146122</v>
       </c>
       <c r="I60" s="3">
-        <v>0.5124231525846958</v>
+        <v>0.5124245782350499</v>
       </c>
       <c r="J60" s="3">
-        <v>0.5124303051049832</v>
+        <v>0.5124317037489395</v>
       </c>
       <c r="K60" s="3">
-        <v>0.5124184419167406</v>
+        <v>0.5124198122543933</v>
       </c>
       <c r="L60" s="3">
-        <v>0.5124637043300054</v>
+        <v>0.512465049173647</v>
       </c>
       <c r="M60" s="3">
-        <v>0.5124517156604337</v>
+        <v>0.5124530327329633</v>
       </c>
       <c r="N60" s="3">
-        <v>0.512459126161113</v>
+        <v>0.5124604158351453</v>
       </c>
       <c r="O60" s="3">
-        <v>0.5124656224761709</v>
+        <v>0.5124668865701495</v>
       </c>
       <c r="P60" s="3">
-        <v>0.5124894706309369</v>
+        <v>0.5124907103517212</v>
       </c>
       <c r="Q60" s="3">
-        <v>0.5124785312535255</v>
+        <v>0.5124797455639066</v>
       </c>
       <c r="R60" s="3" t="s">
         <v>19</v>
@@ -3825,46 +3829,46 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>846407.1749777755</v>
+        <v>846407.1572920395</v>
       </c>
       <c r="F61" s="3">
-        <v>865998.8518851514</v>
+        <v>865997.3506762085</v>
       </c>
       <c r="G61" s="3">
-        <v>882116.2937005755</v>
+        <v>882114.6655821229</v>
       </c>
       <c r="H61" s="3">
-        <v>897727.888135343</v>
+        <v>897726.2592861137</v>
       </c>
       <c r="I61" s="3">
-        <v>916870.2812307647</v>
+        <v>916868.6471696626</v>
       </c>
       <c r="J61" s="3">
-        <v>936400.8782352343</v>
+        <v>936399.2385155612</v>
       </c>
       <c r="K61" s="3">
-        <v>952395.0409367989</v>
+        <v>952393.4081017196</v>
       </c>
       <c r="L61" s="3">
-        <v>975052.207833534</v>
+        <v>975050.5709638221</v>
       </c>
       <c r="M61" s="3">
-        <v>994967.5915141668</v>
+        <v>994965.949334576</v>
       </c>
       <c r="N61" s="3">
-        <v>1014480.722787071</v>
+        <v>1014479.087456928</v>
       </c>
       <c r="O61" s="3">
-        <v>1033999.65852846</v>
+        <v>1033998.024935295</v>
       </c>
       <c r="P61" s="3">
-        <v>1057042.756730865</v>
+        <v>1057041.118943183</v>
       </c>
       <c r="Q61" s="3">
-        <v>1076950.573937892</v>
+        <v>1076948.936869875</v>
       </c>
       <c r="R61" s="3">
-        <v>12450409.92043363</v>
+        <v>12450390.41512711</v>
       </c>
     </row>
     <row r="62" spans="1:18">
@@ -3879,46 +3883,46 @@
         <v>0</v>
       </c>
       <c r="E62" s="3">
-        <v>3028738.164402665</v>
+        <v>3028738.13733732</v>
       </c>
       <c r="F62" s="3">
-        <v>3039601.15557762</v>
+        <v>3039599.127342555</v>
       </c>
       <c r="G62" s="3">
-        <v>3080711.686831542</v>
+        <v>3080707.380532962</v>
       </c>
       <c r="H62" s="3">
-        <v>3131495.540954233</v>
+        <v>3131490.211512017</v>
       </c>
       <c r="I62" s="3">
-        <v>3189420.45509646</v>
+        <v>3189414.739306175</v>
       </c>
       <c r="J62" s="3">
-        <v>3254071.154593993</v>
+        <v>3254065.288600987</v>
       </c>
       <c r="K62" s="3">
-        <v>3317594.108895538</v>
+        <v>3317588.19245248</v>
       </c>
       <c r="L62" s="3">
-        <v>3384703.230112199</v>
+        <v>3384697.29841734</v>
       </c>
       <c r="M62" s="3">
-        <v>3456855.871077524</v>
+        <v>3456849.922783858</v>
       </c>
       <c r="N62" s="3">
-        <v>3527715.288365383</v>
+        <v>3527709.337920835</v>
       </c>
       <c r="O62" s="3">
-        <v>3597595.16489984</v>
+        <v>3597589.221963518</v>
       </c>
       <c r="P62" s="3">
-        <v>3671181.271957956</v>
+        <v>3671175.328889397</v>
       </c>
       <c r="Q62" s="3">
-        <v>3746215.735703005</v>
+        <v>3746209.788848046</v>
       </c>
       <c r="R62" s="3">
-        <v>43425898.82846796</v>
+        <v>43425833.97590749</v>
       </c>
     </row>
     <row r="63" spans="1:18">
@@ -3933,46 +3937,46 @@
         <v>9862402</v>
       </c>
       <c r="E63" s="3">
-        <v>9882026.11617299</v>
+        <v>9882026.078313328</v>
       </c>
       <c r="F63" s="3">
-        <v>9952075.491951328</v>
+        <v>9952071.47172736</v>
       </c>
       <c r="G63" s="3">
-        <v>10048604.05163153</v>
+        <v>10048596.31066858</v>
       </c>
       <c r="H63" s="3">
-        <v>10168086.55226283</v>
+        <v>10168075.7322094</v>
       </c>
       <c r="I63" s="3">
-        <v>10314865.08628714</v>
+        <v>10314851.88500606</v>
       </c>
       <c r="J63" s="3">
-        <v>10483581.94570598</v>
+        <v>10483566.96820293</v>
       </c>
       <c r="K63" s="3">
-        <v>10659544.68988449</v>
+        <v>10659528.4387146</v>
       </c>
       <c r="L63" s="3">
-        <v>10858005.68391906</v>
+        <v>10857988.50967231</v>
       </c>
       <c r="M63" s="3">
-        <v>11066275.32342069</v>
+        <v>11066257.47370458</v>
       </c>
       <c r="N63" s="3">
-        <v>11281084.84143169</v>
+        <v>11281066.52517498</v>
       </c>
       <c r="O63" s="3">
-        <v>11500223.75534087</v>
+        <v>11500205.1118177</v>
       </c>
       <c r="P63" s="3">
-        <v>11731745.67807608</v>
+        <v>11731726.79286203</v>
       </c>
       <c r="Q63" s="3">
-        <v>11964601.69043222</v>
+        <v>11964582.63330548</v>
       </c>
       <c r="R63" s="3">
-        <v>149773122.9065169</v>
+        <v>149772945.9313793</v>
       </c>
     </row>
     <row r="64" spans="1:18">
@@ -4041,46 +4045,46 @@
         <v>0</v>
       </c>
       <c r="E65" s="3">
-        <v>22174869599.65924</v>
+        <v>22174873774.08001</v>
       </c>
       <c r="F65" s="3">
-        <v>21108189681.21271</v>
+        <v>21108647027.04025</v>
       </c>
       <c r="G65" s="3">
-        <v>21460464061.20095</v>
+        <v>21460920501.88671</v>
       </c>
       <c r="H65" s="3">
-        <v>21846916607.4454</v>
+        <v>21847370250.51009</v>
       </c>
       <c r="I65" s="3">
-        <v>22294936881.2272</v>
+        <v>22295391671.88422</v>
       </c>
       <c r="J65" s="3">
-        <v>22774393182.82831</v>
+        <v>22774849256.37924</v>
       </c>
       <c r="K65" s="3">
-        <v>23226510764.90977</v>
+        <v>23226964484.65923</v>
       </c>
       <c r="L65" s="3">
-        <v>23784574066.02527</v>
+        <v>23785028770.53642</v>
       </c>
       <c r="M65" s="3">
-        <v>24313253765.59791</v>
+        <v>24313709973.40934</v>
       </c>
       <c r="N65" s="3">
-        <v>24860968544.32758</v>
+        <v>24861422440.36335</v>
       </c>
       <c r="O65" s="3">
-        <v>25401855947.9487</v>
+        <v>25402309449.66431</v>
       </c>
       <c r="P65" s="3">
-        <v>26002265413.39288</v>
+        <v>26002720088.03078</v>
       </c>
       <c r="Q65" s="3">
-        <v>26565937028.59108</v>
+        <v>26566391470.76495</v>
       </c>
       <c r="R65" s="3">
-        <v>305815135544.3669</v>
+        <v>305820599159.2089</v>
       </c>
     </row>
     <row r="66" spans="1:18">
@@ -4095,46 +4099,46 @@
         <v>0</v>
       </c>
       <c r="E66" s="3">
-        <v>57492345370.27991</v>
+        <v>57492330656.34814</v>
       </c>
       <c r="F66" s="3">
-        <v>57641959176.37731</v>
+        <v>57641971952.32352</v>
       </c>
       <c r="G66" s="3">
-        <v>57735599110.33782</v>
+        <v>57735670638.70547</v>
       </c>
       <c r="H66" s="3">
-        <v>57924435766.67975</v>
+        <v>57924562177.52044</v>
       </c>
       <c r="I66" s="3">
-        <v>58315025691.87732</v>
+        <v>58315193542.85978</v>
       </c>
       <c r="J66" s="3">
-        <v>58914634374.70709</v>
+        <v>58914832028.52785</v>
       </c>
       <c r="K66" s="3">
-        <v>59711883966.10838</v>
+        <v>59712102767.84681</v>
       </c>
       <c r="L66" s="3">
-        <v>60662984751.05671</v>
+        <v>60663218356.80781</v>
       </c>
       <c r="M66" s="3">
-        <v>61732796046.06815</v>
+        <v>61733040052.31509</v>
       </c>
       <c r="N66" s="3">
-        <v>62918797298.4678</v>
+        <v>62919048637.51784</v>
       </c>
       <c r="O66" s="3">
-        <v>64190438495.30525</v>
+        <v>64190694874.63803</v>
       </c>
       <c r="P66" s="3">
-        <v>65517689328.33566</v>
+        <v>65517949178.68291</v>
       </c>
       <c r="Q66" s="3">
-        <v>66895931917.13569</v>
+        <v>66896194211.40559</v>
       </c>
       <c r="R66" s="3">
-        <v>789654521292.7371</v>
+        <v>789656809075.4993</v>
       </c>
     </row>
     <row r="67" spans="1:18">
@@ -4149,46 +4153,46 @@
         <v>0</v>
       </c>
       <c r="E67" s="3">
-        <v>554492316.2241917</v>
+        <v>554491654.1201342</v>
       </c>
       <c r="F67" s="3">
-        <v>557507828.597302</v>
+        <v>557506957.5949601</v>
       </c>
       <c r="G67" s="3">
-        <v>562924998.5849286</v>
+        <v>562923875.9578997</v>
       </c>
       <c r="H67" s="3">
-        <v>569777539.9272223</v>
+        <v>569776230.3191302</v>
       </c>
       <c r="I67" s="3">
-        <v>578070914.272352</v>
+        <v>578069470.0988536</v>
       </c>
       <c r="J67" s="3">
-        <v>587663424.9496313</v>
+        <v>587661883.5021286</v>
       </c>
       <c r="K67" s="3">
-        <v>597749864.027426</v>
+        <v>597748254.4252005</v>
       </c>
       <c r="L67" s="3">
-        <v>608799766.9151007</v>
+        <v>608798108.2711726</v>
       </c>
       <c r="M67" s="3">
-        <v>620622537.5102829</v>
+        <v>620620842.7288345</v>
       </c>
       <c r="N67" s="3">
-        <v>632756081.8394897</v>
+        <v>632754362.387319</v>
       </c>
       <c r="O67" s="3">
-        <v>645088287.1980664</v>
+        <v>645086550.932328</v>
       </c>
       <c r="P67" s="3">
-        <v>658007414.287546</v>
+        <v>658005665.2691336</v>
       </c>
       <c r="Q67" s="3">
-        <v>671175034.1771317</v>
+        <v>671173276.0369809</v>
       </c>
       <c r="R67" s="3">
-        <v>7844636008.510672</v>
+        <v>7844617131.644075</v>
       </c>
     </row>
     <row r="68" spans="1:18">
@@ -4203,46 +4207,46 @@
         <v>0</v>
       </c>
       <c r="E68" s="3">
-        <v>376644912.431653</v>
+        <v>376645921.5124688</v>
       </c>
       <c r="F68" s="3">
-        <v>385318750.8861426</v>
+        <v>385319196.1141558</v>
       </c>
       <c r="G68" s="3">
-        <v>392476277.3621725</v>
+        <v>392476680.5183489</v>
       </c>
       <c r="H68" s="3">
-        <v>399428734.9421546</v>
+        <v>399429140.4191912</v>
       </c>
       <c r="I68" s="3">
-        <v>407967692.7627532</v>
+        <v>407968100.7111775</v>
       </c>
       <c r="J68" s="3">
-        <v>416663781.0783113</v>
+        <v>416664188.717358</v>
       </c>
       <c r="K68" s="3">
-        <v>423770781.4565296</v>
+        <v>423771188.1913379</v>
       </c>
       <c r="L68" s="3">
-        <v>433890472.4877144</v>
+        <v>433890882.7379955</v>
       </c>
       <c r="M68" s="3">
-        <v>442742301.8914395</v>
+        <v>442742709.0594019</v>
       </c>
       <c r="N68" s="3">
-        <v>451431814.8806959</v>
+        <v>451432223.2668582</v>
       </c>
       <c r="O68" s="3">
-        <v>460123341.1412359</v>
+        <v>460123749.1825457</v>
       </c>
       <c r="P68" s="3">
-        <v>470399264.3639284</v>
+        <v>470399673.4268938</v>
       </c>
       <c r="Q68" s="3">
-        <v>479248299.9545809</v>
+        <v>479248707.0213733</v>
       </c>
       <c r="R68" s="3">
-        <v>5540106425.639313</v>
+        <v>5540112360.879107</v>
       </c>
     </row>
     <row r="69" spans="1:18">
@@ -4257,46 +4261,46 @@
         <v>0</v>
       </c>
       <c r="E69" s="3">
-        <v>170903917.2038878</v>
+        <v>170932913.276664</v>
       </c>
       <c r="F69" s="3">
-        <v>178928616.95244</v>
+        <v>178957564.6528735</v>
       </c>
       <c r="G69" s="3">
-        <v>185907132.5987565</v>
+        <v>185935922.9328065</v>
       </c>
       <c r="H69" s="3">
-        <v>192121586.6912931</v>
+        <v>192150357.6025435</v>
       </c>
       <c r="I69" s="3">
-        <v>199196862.4085665</v>
+        <v>199225738.3250566</v>
       </c>
       <c r="J69" s="3">
-        <v>206991964.6766616</v>
+        <v>207020814.819009</v>
       </c>
       <c r="K69" s="3">
-        <v>213890037.8307367</v>
+        <v>213918744.9569666</v>
       </c>
       <c r="L69" s="3">
-        <v>221882517.3780222</v>
+        <v>221911441.3952305</v>
       </c>
       <c r="M69" s="3">
-        <v>230333799.4086777</v>
+        <v>230362578.9266288</v>
       </c>
       <c r="N69" s="3">
-        <v>238095252.454065</v>
+        <v>238124010.9236651</v>
       </c>
       <c r="O69" s="3">
-        <v>245861714.0897993</v>
+        <v>245890451.9030555</v>
       </c>
       <c r="P69" s="3">
-        <v>254571225.1936734</v>
+        <v>254600050.3068004</v>
       </c>
       <c r="Q69" s="3">
-        <v>262944781.5780343</v>
+        <v>262973476.1246122</v>
       </c>
       <c r="R69" s="3">
-        <v>2801629408.464614</v>
+        <v>2802004066.145912</v>
       </c>
     </row>
     <row r="70" spans="1:18">
@@ -4311,46 +4315,46 @@
         <v>0</v>
       </c>
       <c r="E70" s="3">
-        <v>478387521.4454772</v>
+        <v>478394303.7450669</v>
       </c>
       <c r="F70" s="3">
-        <v>488170163.0998313</v>
+        <v>488176945.3994209</v>
       </c>
       <c r="G70" s="3">
-        <v>500398465.1677741</v>
+        <v>500405247.4673638</v>
       </c>
       <c r="H70" s="3">
-        <v>510181106.8221281</v>
+        <v>510187889.1217179</v>
       </c>
       <c r="I70" s="3">
-        <v>519963748.4764825</v>
+        <v>519970530.7760721</v>
       </c>
       <c r="J70" s="3">
-        <v>532192050.5444248</v>
+        <v>532198832.8440149</v>
       </c>
       <c r="K70" s="3">
-        <v>544420352.6123679</v>
+        <v>544427134.9119576</v>
       </c>
       <c r="L70" s="3">
-        <v>554202994.2667222</v>
+        <v>554209776.5663116</v>
       </c>
       <c r="M70" s="3">
-        <v>568876956.7482531</v>
+        <v>568883739.0478432</v>
       </c>
       <c r="N70" s="3">
-        <v>581105258.8161958</v>
+        <v>581112041.1157856</v>
       </c>
       <c r="O70" s="3">
-        <v>593333560.8841387</v>
+        <v>593340343.1837287</v>
       </c>
       <c r="P70" s="3">
-        <v>605561862.9520814</v>
+        <v>605568645.2516714</v>
       </c>
       <c r="Q70" s="3">
-        <v>620235825.4336127</v>
+        <v>620242607.7332029</v>
       </c>
       <c r="R70" s="3">
-        <v>7097029867.26949</v>
+        <v>7097118037.164158</v>
       </c>
     </row>
     <row r="71" spans="1:18">
@@ -4365,46 +4369,46 @@
         <v>0</v>
       </c>
       <c r="E71" s="3">
-        <v>64527.4824831224</v>
+        <v>64534.39529364954</v>
       </c>
       <c r="F71" s="3">
-        <v>66758.60744900139</v>
+        <v>66765.54942119546</v>
       </c>
       <c r="G71" s="3">
-        <v>68864.07600035878</v>
+        <v>68870.98354955023</v>
       </c>
       <c r="H71" s="3">
-        <v>70790.69761033868</v>
+        <v>70797.60295686778</v>
       </c>
       <c r="I71" s="3">
-        <v>73030.32509476029</v>
+        <v>73037.25807117697</v>
       </c>
       <c r="J71" s="3">
-        <v>75441.04053289854</v>
+        <v>75447.97031669036</v>
       </c>
       <c r="K71" s="3">
-        <v>77530.63683984836</v>
+        <v>77537.53506011683</v>
       </c>
       <c r="L71" s="3">
-        <v>80101.47275678733</v>
+        <v>80108.4251601943</v>
       </c>
       <c r="M71" s="3">
-        <v>82668.89939942828</v>
+        <v>82675.82037775483</v>
       </c>
       <c r="N71" s="3">
-        <v>85076.8977592626</v>
+        <v>85083.81603446216</v>
       </c>
       <c r="O71" s="3">
-        <v>87484.31455425375</v>
+        <v>87491.23023109864</v>
       </c>
       <c r="P71" s="3">
-        <v>90226.59781526602</v>
+        <v>90233.53678799063</v>
       </c>
       <c r="Q71" s="3">
-        <v>92778.74420641083</v>
+        <v>92785.65450688318</v>
       </c>
       <c r="R71" s="3">
-        <v>1015279.792501737</v>
+        <v>1015369.777767631</v>
       </c>
     </row>
     <row r="72" spans="1:18">
@@ -4419,46 +4423,46 @@
         <v>0</v>
       </c>
       <c r="E72" s="3">
-        <v>80871063252.2952</v>
+        <v>80871087835.96532</v>
       </c>
       <c r="F72" s="3">
-        <v>79974822224.84706</v>
+        <v>79975327212.56044</v>
       </c>
       <c r="G72" s="3">
-        <v>80445362631.96623</v>
+        <v>80445925057.93379</v>
       </c>
       <c r="H72" s="3">
-        <v>81043503398.26341</v>
+        <v>81044117702.67688</v>
       </c>
       <c r="I72" s="3">
-        <v>81907267128.58702</v>
+        <v>81907923991.20206</v>
       </c>
       <c r="J72" s="3">
-        <v>83015950438.74664</v>
+        <v>83016638264.04256</v>
       </c>
       <c r="K72" s="3">
-        <v>84294532516.12552</v>
+        <v>84295238924.33524</v>
       </c>
       <c r="L72" s="3">
-        <v>85832524197.11459</v>
+        <v>85833246562.00211</v>
       </c>
       <c r="M72" s="3">
-        <v>87465965774.23268</v>
+        <v>87466699862.24811</v>
       </c>
       <c r="N72" s="3">
-        <v>89231807512.8029</v>
+        <v>89232546576.12399</v>
       </c>
       <c r="O72" s="3">
-        <v>91076665489.74051</v>
+        <v>91077409161.55168</v>
       </c>
       <c r="P72" s="3">
-        <v>93038185470.75967</v>
+        <v>93038933861.07808</v>
       </c>
       <c r="Q72" s="3">
-        <v>95016317365.65974</v>
+        <v>95017067827.71985</v>
       </c>
       <c r="R72" s="3">
-        <v>1113213967401.141</v>
+        <v>1113222162839.44</v>
       </c>
     </row>
     <row r="73" spans="1:18">
@@ -4491,46 +4495,46 @@
         <v>0</v>
       </c>
       <c r="E74" s="3">
-        <v>1186210.3224812</v>
+        <v>1186216.516016889</v>
       </c>
       <c r="F74" s="3">
-        <v>1196012.396770856</v>
+        <v>1196019.713658017</v>
       </c>
       <c r="G74" s="3">
-        <v>1208407.579728351</v>
+        <v>1208415.72205119</v>
       </c>
       <c r="H74" s="3">
-        <v>1222705.584120793</v>
+        <v>1222714.312102258</v>
       </c>
       <c r="I74" s="3">
-        <v>1238995.856141571</v>
+        <v>1239005.012695365</v>
       </c>
       <c r="J74" s="3">
-        <v>1257024.43495994</v>
+        <v>1257033.910390874</v>
       </c>
       <c r="K74" s="3">
-        <v>1276855.807699118</v>
+        <v>1276865.524947298</v>
       </c>
       <c r="L74" s="3">
-        <v>1298068.378729621</v>
+        <v>1298078.283821164</v>
       </c>
       <c r="M74" s="3">
-        <v>1320347.42769037</v>
+        <v>1320357.477822137</v>
       </c>
       <c r="N74" s="3">
-        <v>1343971.539317583</v>
+        <v>1343981.704580372</v>
       </c>
       <c r="O74" s="3">
-        <v>1368571.140387328</v>
+        <v>1368581.399209833</v>
       </c>
       <c r="P74" s="3">
-        <v>1393740.509035077</v>
+        <v>1393750.843770748</v>
       </c>
       <c r="Q74" s="3">
-        <v>1419517.463935521</v>
+        <v>1419527.859706078</v>
       </c>
       <c r="R74" s="3">
-        <v>16730428.44099733</v>
+        <v>16730548.28077222</v>
       </c>
     </row>
     <row r="75" spans="1:18">
@@ -4545,46 +4549,46 @@
         <v>0</v>
       </c>
       <c r="E75" s="3">
-        <v>193174.2370408868</v>
+        <v>193174.1016733081</v>
       </c>
       <c r="F75" s="3">
-        <v>178367.0387382079</v>
+        <v>178366.8855807222</v>
       </c>
       <c r="G75" s="3">
-        <v>181428.6188933844</v>
+        <v>181428.453867164</v>
       </c>
       <c r="H75" s="3">
-        <v>184818.8785536569</v>
+        <v>184818.7048207248</v>
       </c>
       <c r="I75" s="3">
-        <v>188704.0918862988</v>
+        <v>188703.9117305795</v>
       </c>
       <c r="J75" s="3">
-        <v>192865.3694440791</v>
+        <v>192865.1842914546</v>
       </c>
       <c r="K75" s="3">
-        <v>196834.0775555172</v>
+        <v>196833.8882921082</v>
       </c>
       <c r="L75" s="3">
-        <v>201689.5135166289</v>
+        <v>201689.3211613583</v>
       </c>
       <c r="M75" s="3">
-        <v>206283.1254086139</v>
+        <v>206282.9303528801</v>
       </c>
       <c r="N75" s="3">
-        <v>211089.9453916771</v>
+        <v>211089.7480196512</v>
       </c>
       <c r="O75" s="3">
-        <v>215814.7811773755</v>
+        <v>215814.5818522288</v>
       </c>
       <c r="P75" s="3">
-        <v>221041.0584348564</v>
+        <v>221040.8575335175</v>
       </c>
       <c r="Q75" s="3">
-        <v>225963.780493779</v>
+        <v>225963.5780747093</v>
       </c>
       <c r="R75" s="3">
-        <v>2598074.516534962</v>
+        <v>2598072.147250406</v>
       </c>
     </row>
     <row r="76" spans="1:18">
@@ -4599,46 +4603,46 @@
         <v>0</v>
       </c>
       <c r="E76" s="3">
-        <v>750523.2698388123</v>
+        <v>750517.0992347258</v>
       </c>
       <c r="F76" s="3">
-        <v>749726.4123938991</v>
+        <v>749719.1577583415</v>
       </c>
       <c r="G76" s="3">
-        <v>748218.8307592855</v>
+        <v>748210.7815943821</v>
       </c>
       <c r="H76" s="3">
-        <v>748522.9334733336</v>
+        <v>748514.3219487155</v>
       </c>
       <c r="I76" s="3">
-        <v>752064.1406374259</v>
+        <v>752055.1184495734</v>
       </c>
       <c r="J76" s="3">
-        <v>758809.7075613047</v>
+        <v>758800.3805427576</v>
       </c>
       <c r="K76" s="3">
-        <v>768487.2850140631</v>
+        <v>768477.7273305978</v>
       </c>
       <c r="L76" s="3">
-        <v>780427.7503506693</v>
+        <v>780418.0137593773</v>
       </c>
       <c r="M76" s="3">
-        <v>794105.4315139514</v>
+        <v>794095.5570782393</v>
       </c>
       <c r="N76" s="3">
-        <v>809436.1237609683</v>
+        <v>809426.1400198918</v>
       </c>
       <c r="O76" s="3">
-        <v>825984.6019656369</v>
+        <v>825974.5294244719</v>
       </c>
       <c r="P76" s="3">
-        <v>843331.6644441279</v>
+        <v>843321.5199102225</v>
       </c>
       <c r="Q76" s="3">
-        <v>861399.9602471227</v>
+        <v>861389.7579227475</v>
       </c>
       <c r="R76" s="3">
-        <v>10191038.1119606</v>
+        <v>10190920.10497404</v>
       </c>
     </row>
     <row r="77" spans="1:18">
@@ -4653,46 +4657,46 @@
         <v>0</v>
       </c>
       <c r="E77" s="3">
-        <v>56279.60057265951</v>
+        <v>56278.96468354583</v>
       </c>
       <c r="F77" s="3">
-        <v>56559.54446310477</v>
+        <v>56558.90980461649</v>
       </c>
       <c r="G77" s="3">
-        <v>56894.3464178631</v>
+        <v>56893.7121452564</v>
       </c>
       <c r="H77" s="3">
-        <v>57349.54858622327</v>
+        <v>57348.91531688736</v>
       </c>
       <c r="I77" s="3">
-        <v>57965.14672644515</v>
+        <v>57964.51399777604</v>
       </c>
       <c r="J77" s="3">
-        <v>58732.54405259105</v>
+        <v>58731.91151365856</v>
       </c>
       <c r="K77" s="3">
-        <v>59645.33341443977</v>
+        <v>59644.70076740347</v>
       </c>
       <c r="L77" s="3">
-        <v>60668.31306517965</v>
+        <v>60667.67981565107</v>
       </c>
       <c r="M77" s="3">
-        <v>61777.86777049008</v>
+        <v>61777.23385996009</v>
       </c>
       <c r="N77" s="3">
-        <v>62979.65177815052</v>
+        <v>62979.01710651947</v>
       </c>
       <c r="O77" s="3">
-        <v>64247.91758551401</v>
+        <v>64247.28193043387</v>
       </c>
       <c r="P77" s="3">
-        <v>65557.75297058214</v>
+        <v>65557.11622854031</v>
       </c>
       <c r="Q77" s="3">
-        <v>66909.22919973756</v>
+        <v>66908.59149794368</v>
       </c>
       <c r="R77" s="3">
-        <v>785566.7966029805</v>
+        <v>785558.5486681925</v>
       </c>
     </row>
     <row r="78" spans="1:18">
@@ -4707,46 +4711,46 @@
         <v>0</v>
       </c>
       <c r="E78" s="3">
-        <v>405373.7193493457</v>
+        <v>405375.5121195008</v>
       </c>
       <c r="F78" s="3">
-        <v>407262.1212096437</v>
+        <v>407263.920659504</v>
       </c>
       <c r="G78" s="3">
-        <v>409544.548571715</v>
+        <v>409546.3545987337</v>
       </c>
       <c r="H78" s="3">
-        <v>412606.8546570395</v>
+        <v>412608.6623912671</v>
       </c>
       <c r="I78" s="3">
-        <v>416765.3265532721</v>
+        <v>416767.1351822296</v>
       </c>
       <c r="J78" s="3">
-        <v>421959.8948869369</v>
+        <v>421961.7038197358</v>
       </c>
       <c r="K78" s="3">
-        <v>428146.9729813065</v>
+        <v>428148.7818598442</v>
       </c>
       <c r="L78" s="3">
-        <v>435097.5857481564</v>
+        <v>435099.3952441327</v>
       </c>
       <c r="M78" s="3">
-        <v>442635.9816007765</v>
+        <v>442637.7912936249</v>
       </c>
       <c r="N78" s="3">
-        <v>450802.8417048227</v>
+        <v>450804.6514423375</v>
       </c>
       <c r="O78" s="3">
-        <v>459429.2627331536</v>
+        <v>459431.0729468529</v>
       </c>
       <c r="P78" s="3">
-        <v>468342.4019691955</v>
+        <v>468344.2128778718</v>
       </c>
       <c r="Q78" s="3">
-        <v>477534.2147382734</v>
+        <v>477536.0259173677</v>
       </c>
       <c r="R78" s="3">
-        <v>5635501.726703638</v>
+        <v>5635525.220353003</v>
       </c>
     </row>
     <row r="79" spans="1:18">
@@ -4761,46 +4765,46 @@
         <v>0</v>
       </c>
       <c r="E79" s="3">
-        <v>1531359.872970667</v>
+        <v>1531358.103132114</v>
       </c>
       <c r="F79" s="3">
-        <v>1538476.687955111</v>
+        <v>1538474.950756854</v>
       </c>
       <c r="G79" s="3">
-        <v>1547081.861915921</v>
+        <v>1547080.149046839</v>
       </c>
       <c r="H79" s="3">
-        <v>1558621.662937087</v>
+        <v>1558619.971659706</v>
       </c>
       <c r="I79" s="3">
-        <v>1574294.670225725</v>
+        <v>1574292.995962709</v>
       </c>
       <c r="J79" s="3">
-        <v>1593874.247634307</v>
+        <v>1593872.587113896</v>
       </c>
       <c r="K79" s="3">
-        <v>1617196.119731875</v>
+        <v>1617194.470418052</v>
       </c>
       <c r="L79" s="3">
-        <v>1643398.543332134</v>
+        <v>1643396.902336408</v>
       </c>
       <c r="M79" s="3">
-        <v>1671816.877603545</v>
+        <v>1671815.243606752</v>
       </c>
       <c r="N79" s="3">
-        <v>1702604.821373729</v>
+        <v>1702603.193157926</v>
       </c>
       <c r="O79" s="3">
-        <v>1735126.479619812</v>
+        <v>1735124.855687452</v>
       </c>
       <c r="P79" s="3">
-        <v>1768729.77151001</v>
+        <v>1768728.150803098</v>
       </c>
       <c r="Q79" s="3">
-        <v>1803383.20944437</v>
+        <v>1803381.591711458</v>
       </c>
       <c r="R79" s="3">
-        <v>21285964.82625429</v>
+        <v>21285943.16539326</v>
       </c>
     </row>
     <row r="80" spans="1:18">
@@ -4815,46 +4819,46 @@
         <v>0</v>
       </c>
       <c r="E80" s="3">
-        <v>1880453.991747353</v>
+        <v>1880454.650568069</v>
       </c>
       <c r="F80" s="3">
-        <v>1889179.26470165</v>
+        <v>1889179.961611742</v>
       </c>
       <c r="G80" s="3">
-        <v>1899732.064069773</v>
+        <v>1899732.791500316</v>
       </c>
       <c r="H80" s="3">
-        <v>1913878.969007903</v>
+        <v>1913879.718734087</v>
       </c>
       <c r="I80" s="3">
-        <v>1933094.850052552</v>
+        <v>1933095.617147162</v>
       </c>
       <c r="J80" s="3">
-        <v>1957101.598468653</v>
+        <v>1957102.379419973</v>
       </c>
       <c r="K80" s="3">
-        <v>1985697.759298742</v>
+        <v>1985698.551510492</v>
       </c>
       <c r="L80" s="3">
-        <v>2017827.816015111</v>
+        <v>2017828.61776489</v>
       </c>
       <c r="M80" s="3">
-        <v>2052674.991433832</v>
+        <v>2052675.801040417</v>
       </c>
       <c r="N80" s="3">
-        <v>2090428.011300401</v>
+        <v>2090428.827493744</v>
       </c>
       <c r="O80" s="3">
-        <v>2130307.824767451</v>
+        <v>2130308.646703871</v>
       </c>
       <c r="P80" s="3">
-        <v>2171514.420508624</v>
+        <v>2171515.24745243</v>
       </c>
       <c r="Q80" s="3">
-        <v>2214008.194982906</v>
+        <v>2214009.026130882</v>
       </c>
       <c r="R80" s="3">
-        <v>26135899.75635495</v>
+        <v>26135909.83707808</v>
       </c>
     </row>
     <row r="81" spans="1:18">
@@ -4869,46 +4873,46 @@
         <v>0</v>
       </c>
       <c r="E81" s="3">
-        <v>910671.8312466616</v>
+        <v>910675.831114114</v>
       </c>
       <c r="F81" s="3">
-        <v>918186.0466746051</v>
+        <v>918190.9070650158</v>
       </c>
       <c r="G81" s="3">
-        <v>927690.833650767</v>
+        <v>927696.3242651257</v>
       </c>
       <c r="H81" s="3">
-        <v>938648.795157689</v>
+        <v>938654.7337166941</v>
       </c>
       <c r="I81" s="3">
-        <v>951131.0270758929</v>
+        <v>951137.2937437339</v>
       </c>
       <c r="J81" s="3">
-        <v>964942.760155238</v>
+        <v>964949.2715431375</v>
       </c>
       <c r="K81" s="3">
-        <v>980133.7762591615</v>
+        <v>980140.4738654094</v>
       </c>
       <c r="L81" s="3">
-        <v>996382.595255569</v>
+        <v>996389.4377054609</v>
       </c>
       <c r="M81" s="3">
-        <v>1013447.150116333</v>
+        <v>1013454.104976935</v>
       </c>
       <c r="N81" s="3">
-        <v>1031541.34294544</v>
+        <v>1031548.387483835</v>
       </c>
       <c r="O81" s="3">
-        <v>1050382.904288544</v>
+        <v>1050390.021842009</v>
       </c>
       <c r="P81" s="3">
-        <v>1069660.934978853</v>
+        <v>1069668.111932933</v>
       </c>
       <c r="Q81" s="3">
-        <v>1089403.735451495</v>
+        <v>1089410.960569768</v>
       </c>
       <c r="R81" s="3">
-        <v>12842223.73325625</v>
+        <v>12842305.85982417</v>
       </c>
     </row>
     <row r="82" spans="1:18">
@@ -4923,43 +4927,43 @@
         <v>0.3411657413950535</v>
       </c>
       <c r="E82" s="3">
-        <v>0.3325572064886703</v>
+        <v>0.3325545037201402</v>
       </c>
       <c r="F82" s="3">
-        <v>0.328588059094065</v>
+        <v>0.328585084588879</v>
       </c>
       <c r="G82" s="3">
-        <v>0.3259257327991586</v>
+        <v>0.3259225795464434</v>
       </c>
       <c r="H82" s="3">
-        <v>0.3242451783179372</v>
+        <v>0.3242419132764908</v>
       </c>
       <c r="I82" s="3">
-        <v>0.3231431818525964</v>
+        <v>0.3231398535110022</v>
       </c>
       <c r="J82" s="3">
-        <v>0.3225939262984405</v>
+        <v>0.3225905686300382</v>
       </c>
       <c r="K82" s="3">
-        <v>0.3225871972212352</v>
+        <v>0.3225838325256075</v>
       </c>
       <c r="L82" s="3">
-        <v>0.3225993574271989</v>
+        <v>0.3225960063792717</v>
       </c>
       <c r="M82" s="3">
-        <v>0.3229552638231606</v>
+        <v>0.3229519376772483</v>
       </c>
       <c r="N82" s="3">
-        <v>0.32347709473038</v>
+        <v>0.323473802266091</v>
       </c>
       <c r="O82" s="3">
-        <v>0.3240878435238068</v>
+        <v>0.3240845905702934</v>
       </c>
       <c r="P82" s="3">
-        <v>0.3246410231801484</v>
+        <v>0.3246378154837072</v>
       </c>
       <c r="Q82" s="3">
-        <v>0.32536444551651</v>
+        <v>0.3253612845454182</v>
       </c>
       <c r="R82" s="3" t="s">
         <v>19</v>
@@ -4977,43 +4981,43 @@
         <v>0.04535037632743646</v>
       </c>
       <c r="E83" s="3">
-        <v>0.0442100514977713</v>
+        <v>0.04420970755542839</v>
       </c>
       <c r="F83" s="3">
-        <v>0.0443367921273974</v>
+        <v>0.04433645044471565</v>
       </c>
       <c r="G83" s="3">
-        <v>0.04445931952794555</v>
+        <v>0.04445897943509583</v>
       </c>
       <c r="H83" s="3">
-        <v>0.0445612966504788</v>
+        <v>0.04456095909116627</v>
       </c>
       <c r="I83" s="3">
-        <v>0.04467186218574887</v>
+        <v>0.04467152795326559</v>
       </c>
       <c r="J83" s="3">
-        <v>0.04477158380684109</v>
+        <v>0.04477125347530535</v>
       </c>
       <c r="K83" s="3">
-        <v>0.04482750131244758</v>
+        <v>0.0448271753301635</v>
       </c>
       <c r="L83" s="3">
-        <v>0.04491658854070822</v>
+        <v>0.04491626740273916</v>
       </c>
       <c r="M83" s="3">
-        <v>0.04498180204065488</v>
+        <v>0.04498148583516814</v>
       </c>
       <c r="N83" s="3">
-        <v>0.04503006646470437</v>
+        <v>0.04502975545542978</v>
       </c>
       <c r="O83" s="3">
-        <v>0.04507006486730072</v>
+        <v>0.04506975911468712</v>
       </c>
       <c r="P83" s="3">
-        <v>0.04512920876125269</v>
+        <v>0.04512890831380774</v>
       </c>
       <c r="Q83" s="3">
-        <v>0.04516469143412431</v>
+        <v>0.04516439620535104</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>19</v>
@@ -5031,43 +5035,43 @@
         <v>0.2195512735036556</v>
       </c>
       <c r="E84" s="3">
-        <v>0.2268095013950892</v>
+        <v>0.2268106020728837</v>
       </c>
       <c r="F84" s="3">
-        <v>0.2264329147281622</v>
+        <v>0.2264340060355661</v>
       </c>
       <c r="G84" s="3">
-        <v>0.226460707788072</v>
+        <v>0.2264617933883674</v>
       </c>
       <c r="H84" s="3">
-        <v>0.2265336130537424</v>
+        <v>0.2265346886665163</v>
       </c>
       <c r="I84" s="3">
-        <v>0.2265636927945744</v>
+        <v>0.2265647557574083</v>
       </c>
       <c r="J84" s="3">
-        <v>0.2266188429472639</v>
+        <v>0.2266198912397994</v>
       </c>
       <c r="K84" s="3">
-        <v>0.226706308598007</v>
+        <v>0.2267073404569666</v>
       </c>
       <c r="L84" s="3">
-        <v>0.2266805258672661</v>
+        <v>0.2266815402278864</v>
       </c>
       <c r="M84" s="3">
-        <v>0.2267379661515989</v>
+        <v>0.2267389626495709</v>
       </c>
       <c r="N84" s="3">
-        <v>0.226774182158531</v>
+        <v>0.2267751599563608</v>
       </c>
       <c r="O84" s="3">
-        <v>0.2267938332524957</v>
+        <v>0.2267947924064212</v>
       </c>
       <c r="P84" s="3">
-        <v>0.2267760065231076</v>
+        <v>0.2267769472602568</v>
       </c>
       <c r="Q84" s="3">
-        <v>0.2268179322748123</v>
+        <v>0.2268188548340532</v>
       </c>
       <c r="R84" s="3" t="s">
         <v>19</v>
@@ -5247,46 +5251,46 @@
         <v>0</v>
       </c>
       <c r="E88" s="3">
-        <v>2113977.836789322</v>
+        <v>2114037.090511756</v>
       </c>
       <c r="F88" s="3">
-        <v>2194792.583609393</v>
+        <v>2194851.775076747</v>
       </c>
       <c r="G88" s="3">
-        <v>2278981.473223276</v>
+        <v>2279040.686889304</v>
       </c>
       <c r="H88" s="3">
-        <v>2365308.413815781</v>
+        <v>2365367.609968731</v>
       </c>
       <c r="I88" s="3">
-        <v>2450584.390781547</v>
+        <v>2450643.48906471</v>
       </c>
       <c r="J88" s="3">
-        <v>2537519.224502246</v>
+        <v>2537578.293875755</v>
       </c>
       <c r="K88" s="3">
-        <v>2629377.716309054</v>
+        <v>2629436.828774147</v>
       </c>
       <c r="L88" s="3">
-        <v>2720122.522798725</v>
+        <v>2720181.540407467</v>
       </c>
       <c r="M88" s="3">
-        <v>2814690.287869317</v>
+        <v>2814749.324744729</v>
       </c>
       <c r="N88" s="3">
-        <v>2912345.45844386</v>
+        <v>2912404.495305041</v>
       </c>
       <c r="O88" s="3">
-        <v>3012679.074615691</v>
+        <v>3012738.102848617</v>
       </c>
       <c r="P88" s="3">
-        <v>3112769.014186066</v>
+        <v>3112827.977464715</v>
       </c>
       <c r="Q88" s="3">
-        <v>3216534.371634894</v>
+        <v>3216593.345055969</v>
       </c>
       <c r="R88" s="3">
-        <v>34359682.36857918</v>
+        <v>34360450.55998769</v>
       </c>
     </row>
     <row r="89" spans="1:18">
@@ -5301,43 +5305,43 @@
         <v>0.1886948075946863</v>
       </c>
       <c r="E89" s="3">
-        <v>0.1868317130048312</v>
+        <v>0.1868369498026214</v>
       </c>
       <c r="F89" s="3">
-        <v>0.1869171219122838</v>
+        <v>0.1869221628891862</v>
       </c>
       <c r="G89" s="3">
-        <v>0.1869855530446633</v>
+        <v>0.1869904113992485</v>
       </c>
       <c r="H89" s="3">
-        <v>0.1870413201824609</v>
+        <v>0.1870460012323117</v>
       </c>
       <c r="I89" s="3">
-        <v>0.1870870093383769</v>
+        <v>0.1870915211279303</v>
       </c>
       <c r="J89" s="3">
-        <v>0.1871238050654567</v>
+        <v>0.1871281610072076</v>
       </c>
       <c r="K89" s="3">
-        <v>0.1871592531791755</v>
+        <v>0.1871634608077531</v>
       </c>
       <c r="L89" s="3">
-        <v>0.1872027660032342</v>
+        <v>0.1872068276804222</v>
       </c>
       <c r="M89" s="3">
-        <v>0.1872432562224154</v>
+        <v>0.1872471835663356</v>
       </c>
       <c r="N89" s="3">
-        <v>0.1872866628808788</v>
+        <v>0.1872904594142487</v>
       </c>
       <c r="O89" s="3">
-        <v>0.1873285783004889</v>
+        <v>0.1873322486798024</v>
       </c>
       <c r="P89" s="3">
-        <v>0.1873643362696695</v>
+        <v>0.1873678853976382</v>
       </c>
       <c r="Q89" s="3">
-        <v>0.187387608618634</v>
+        <v>0.1873910442692662</v>
       </c>
       <c r="R89" s="3" t="s">
         <v>19</v>
@@ -5355,46 +5359,46 @@
         <v>0</v>
       </c>
       <c r="E90" s="3">
-        <v>89.84848234459852</v>
+        <v>89.84841938293401</v>
       </c>
       <c r="F90" s="3">
-        <v>85.41178753542408</v>
+        <v>85.41172120782306</v>
       </c>
       <c r="G90" s="3">
-        <v>83.91045442677986</v>
+        <v>83.91038560260915</v>
       </c>
       <c r="H90" s="3">
-        <v>83.17799021715176</v>
+        <v>83.17791949739788</v>
       </c>
       <c r="I90" s="3">
-        <v>82.7225772421817</v>
+        <v>82.72250514933025</v>
       </c>
       <c r="J90" s="3">
-        <v>82.42696867131914</v>
+        <v>82.42689557908345</v>
       </c>
       <c r="K90" s="3">
-        <v>82.26201950700195</v>
+        <v>82.26194564100385</v>
       </c>
       <c r="L90" s="3">
-        <v>82.1364624257933</v>
+        <v>82.13638806371318</v>
       </c>
       <c r="M90" s="3">
-        <v>82.06401480424911</v>
+        <v>82.06394011281769</v>
       </c>
       <c r="N90" s="3">
-        <v>82.03708759766643</v>
+        <v>82.03701270834893</v>
       </c>
       <c r="O90" s="3">
-        <v>82.03927069436791</v>
+        <v>82.03919571480471</v>
       </c>
       <c r="P90" s="3">
-        <v>82.05156471951516</v>
+        <v>82.05148976740563</v>
       </c>
       <c r="Q90" s="3">
-        <v>82.08766244976184</v>
+        <v>82.08758759085012</v>
       </c>
       <c r="R90" s="3">
-        <v>1082.176342635811</v>
+        <v>1082.175406018122</v>
       </c>
     </row>
     <row r="91" spans="1:18">
@@ -5409,43 +5413,43 @@
         <v>0.01226890863757641</v>
       </c>
       <c r="E91" s="3">
-        <v>0.01184771961693994</v>
+        <v>0.01184772222214626</v>
       </c>
       <c r="F91" s="3">
-        <v>0.01191337932120023</v>
+        <v>0.01191338266238206</v>
       </c>
       <c r="G91" s="3">
-        <v>0.01195688288476349</v>
+        <v>0.01195688624398531</v>
       </c>
       <c r="H91" s="3">
-        <v>0.0119894512780035</v>
+        <v>0.01198945460039844</v>
       </c>
       <c r="I91" s="3">
-        <v>0.01202692856500377</v>
+        <v>0.01202693189228614</v>
       </c>
       <c r="J91" s="3">
-        <v>0.0120587769024002</v>
+        <v>0.01205878014971845</v>
       </c>
       <c r="K91" s="3">
-        <v>0.01207232383831292</v>
+        <v>0.01207232686904249</v>
       </c>
       <c r="L91" s="3">
-        <v>0.01210378521203637</v>
+        <v>0.01210378821837302</v>
       </c>
       <c r="M91" s="3">
-        <v>0.01212212002303964</v>
+        <v>0.01212212284715241</v>
       </c>
       <c r="N91" s="3">
-        <v>0.01213499211348698</v>
+        <v>0.01213499476166432</v>
       </c>
       <c r="O91" s="3">
-        <v>0.01214565295557669</v>
+        <v>0.01214565543652875</v>
       </c>
       <c r="P91" s="3">
-        <v>0.01216540736909739</v>
+        <v>0.01216540976495788</v>
       </c>
       <c r="Q91" s="3">
-        <v>0.01217333298077689</v>
+        <v>0.01217333519331469</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>19</v>
@@ -5463,43 +5467,43 @@
         <v>0.03308146768986005</v>
       </c>
       <c r="E92" s="3">
-        <v>0.03236233188083136</v>
+        <v>0.03236198533328213</v>
       </c>
       <c r="F92" s="3">
-        <v>0.03242341280619716</v>
+        <v>0.03242306778233359</v>
       </c>
       <c r="G92" s="3">
-        <v>0.03250243664318206</v>
+        <v>0.03250209319111052</v>
       </c>
       <c r="H92" s="3">
-        <v>0.0325718453724753</v>
+        <v>0.03257150449076783</v>
       </c>
       <c r="I92" s="3">
-        <v>0.0326449336207451</v>
+        <v>0.03264459606097946</v>
       </c>
       <c r="J92" s="3">
-        <v>0.03271280690444089</v>
+        <v>0.0327124733255869</v>
       </c>
       <c r="K92" s="3">
-        <v>0.03275517747413466</v>
+        <v>0.03275484846112102</v>
       </c>
       <c r="L92" s="3">
-        <v>0.03281280332867186</v>
+        <v>0.03281247918436615</v>
       </c>
       <c r="M92" s="3">
-        <v>0.03285968201761524</v>
+        <v>0.03285936298801574</v>
       </c>
       <c r="N92" s="3">
-        <v>0.03289507435121738</v>
+        <v>0.03289476069376546</v>
       </c>
       <c r="O92" s="3">
-        <v>0.03292441191172404</v>
+        <v>0.03292410367815837</v>
       </c>
       <c r="P92" s="3">
-        <v>0.0329638013921553</v>
+        <v>0.03296349854884986</v>
       </c>
       <c r="Q92" s="3">
-        <v>0.03299135845334742</v>
+        <v>0.03299106101203635</v>
       </c>
       <c r="R92" s="3" t="s">
         <v>19</v>
@@ -5517,43 +5521,43 @@
         <v>121000.9090850509</v>
       </c>
       <c r="E93" s="3">
-        <v>117085.0200497755</v>
+        <v>117085.0471278219</v>
       </c>
       <c r="F93" s="3">
-        <v>118638.0575165667</v>
+        <v>118638.093211842</v>
       </c>
       <c r="G93" s="3">
-        <v>120290.2269703342</v>
+        <v>120290.2640558816</v>
       </c>
       <c r="H93" s="3">
-        <v>122103.9995658255</v>
+        <v>122104.0373883739</v>
       </c>
       <c r="I93" s="3">
-        <v>124292.5555448088</v>
+        <v>124292.5944801806</v>
       </c>
       <c r="J93" s="3">
-        <v>126687.3672506803</v>
+        <v>126687.4063710185</v>
       </c>
       <c r="K93" s="3">
-        <v>128976.4237384039</v>
+        <v>128976.4614863871</v>
       </c>
       <c r="L93" s="3">
-        <v>131731.0559547393</v>
+        <v>131731.094345554</v>
       </c>
       <c r="M93" s="3">
-        <v>134467.3256384602</v>
+        <v>134467.3628803051</v>
       </c>
       <c r="N93" s="3">
-        <v>137225.2320002993</v>
+        <v>137225.2680598538</v>
       </c>
       <c r="O93" s="3">
-        <v>140013.3306108494</v>
+        <v>140013.3654880692</v>
       </c>
       <c r="P93" s="3">
-        <v>143062.0536300468</v>
+        <v>143062.0882222858</v>
       </c>
       <c r="Q93" s="3">
-        <v>145993.0894992128</v>
+        <v>145993.1225648191</v>
       </c>
       <c r="R93" s="3" t="s">
         <v>19</v>
@@ -5571,43 +5575,43 @@
         <v>326262.7331074112</v>
       </c>
       <c r="E94" s="3">
-        <v>319820.5561606039</v>
+        <v>319817.1350451201</v>
       </c>
       <c r="F94" s="3">
-        <v>322884.9354724874</v>
+        <v>322881.5061838399</v>
       </c>
       <c r="G94" s="3">
-        <v>326985.34547657</v>
+        <v>326981.8991791654</v>
       </c>
       <c r="H94" s="3">
-        <v>331720.9854729184</v>
+        <v>331717.5246657287</v>
       </c>
       <c r="I94" s="3">
-        <v>337369.7784419977</v>
+        <v>337366.302271905</v>
       </c>
       <c r="J94" s="3">
-        <v>343674.936160284</v>
+        <v>343671.4452163297</v>
       </c>
       <c r="K94" s="3">
-        <v>349944.6921828929</v>
+        <v>349941.1916911835</v>
       </c>
       <c r="L94" s="3">
-        <v>357116.8155745807</v>
+        <v>357113.3031381045</v>
       </c>
       <c r="M94" s="3">
-        <v>364503.3668896938</v>
+        <v>364499.8440156154</v>
       </c>
       <c r="N94" s="3">
-        <v>371984.9314525672</v>
+        <v>371981.4011149692</v>
       </c>
       <c r="O94" s="3">
-        <v>379547.8585650998</v>
+        <v>379544.3223090941</v>
       </c>
       <c r="P94" s="3">
-        <v>387645.8041671502</v>
+        <v>387642.2601969851</v>
       </c>
       <c r="Q94" s="3">
-        <v>395660.7738395057</v>
+        <v>395657.2243668064</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>19</v>
@@ -5679,43 +5683,43 @@
         <v>0.5092287374537772</v>
       </c>
       <c r="E96" s="3">
-        <v>0.5143782494419064</v>
+        <v>0.5143726194475871</v>
       </c>
       <c r="F96" s="3">
-        <v>0.5141788283228185</v>
+        <v>0.5141732088718671</v>
       </c>
       <c r="G96" s="3">
-        <v>0.5141337126624381</v>
+        <v>0.5141281535413167</v>
       </c>
       <c r="H96" s="3">
-        <v>0.5141149685402143</v>
+        <v>0.5141094962720103</v>
       </c>
       <c r="I96" s="3">
-        <v>0.5141133724084026</v>
+        <v>0.5141079927878219</v>
       </c>
       <c r="J96" s="3">
-        <v>0.5140879014223271</v>
+        <v>0.5140826247955724</v>
       </c>
       <c r="K96" s="3">
-        <v>0.5140427144688428</v>
+        <v>0.5140375443024716</v>
       </c>
       <c r="L96" s="3">
-        <v>0.5140582620932522</v>
+        <v>0.5140531872947985</v>
       </c>
       <c r="M96" s="3">
-        <v>0.5140124136385005</v>
+        <v>0.5140074449039805</v>
       </c>
       <c r="N96" s="3">
-        <v>0.5139880775169736</v>
+        <v>0.5139832109896728</v>
       </c>
       <c r="O96" s="3">
-        <v>0.5139643006758098</v>
+        <v>0.513959530488075</v>
       </c>
       <c r="P96" s="3">
-        <v>0.5139592486201771</v>
+        <v>0.5139545703105306</v>
       </c>
       <c r="Q96" s="3">
-        <v>0.5139178829104377</v>
+        <v>0.5139133008384638</v>
       </c>
       <c r="R96" s="3" t="s">
         <v>19</v>
@@ -5733,46 +5737,46 @@
         <v>0</v>
       </c>
       <c r="E97" s="3">
-        <v>846445.2550969757</v>
+        <v>846445.2350107228</v>
       </c>
       <c r="F97" s="3">
-        <v>868082.8138815481</v>
+        <v>868082.7923303905</v>
       </c>
       <c r="G97" s="3">
-        <v>884375.4237888249</v>
+        <v>884375.401923444</v>
       </c>
       <c r="H97" s="3">
-        <v>899988.1061551964</v>
+        <v>899988.0841758739</v>
       </c>
       <c r="I97" s="3">
-        <v>919137.766791902</v>
+        <v>919137.7446870989</v>
       </c>
       <c r="J97" s="3">
-        <v>938676.2243317793</v>
+        <v>938676.2021316688</v>
       </c>
       <c r="K97" s="3">
-        <v>954660.8896767811</v>
+        <v>954660.8674809207</v>
       </c>
       <c r="L97" s="3">
-        <v>977323.6859099158</v>
+        <v>977323.6636079018</v>
       </c>
       <c r="M97" s="3">
-        <v>997246.4105178828</v>
+        <v>997246.3881758827</v>
       </c>
       <c r="N97" s="3">
-        <v>1016750.101038935</v>
+        <v>1016750.078689167</v>
       </c>
       <c r="O97" s="3">
-        <v>1036266.641811359</v>
+        <v>1036266.619455771</v>
       </c>
       <c r="P97" s="3">
-        <v>1059315.560335694</v>
+        <v>1059315.5379168</v>
       </c>
       <c r="Q97" s="3">
-        <v>1079222.379526435</v>
+        <v>1079222.357109398</v>
       </c>
       <c r="R97" s="3">
-        <v>12477491.25886323</v>
+        <v>12477490.97269504</v>
       </c>
     </row>
     <row r="98" spans="1:18">
@@ -5787,46 +5791,46 @@
         <v>0</v>
       </c>
       <c r="E98" s="3">
-        <v>3028922.479138133</v>
+        <v>3028922.488820953</v>
       </c>
       <c r="F98" s="3">
-        <v>3042613.849974125</v>
+        <v>3042613.84767731</v>
       </c>
       <c r="G98" s="3">
-        <v>3086892.353030062</v>
+        <v>3086892.344063326</v>
       </c>
       <c r="H98" s="3">
-        <v>3139098.054335712</v>
+        <v>3139098.042923963</v>
       </c>
       <c r="I98" s="3">
-        <v>3197560.99313408</v>
+        <v>3197560.981122244</v>
       </c>
       <c r="J98" s="3">
-        <v>3262422.086525716</v>
+        <v>3262422.074614744</v>
       </c>
       <c r="K98" s="3">
-        <v>3326016.930152114</v>
+        <v>3326016.918641494</v>
       </c>
       <c r="L98" s="3">
-        <v>3393148.860511717</v>
+        <v>3393148.849410112</v>
       </c>
       <c r="M98" s="3">
-        <v>3465326.119396412</v>
+        <v>3465326.108692355</v>
       </c>
       <c r="N98" s="3">
-        <v>3536189.98154472</v>
+        <v>3536189.971257767</v>
       </c>
       <c r="O98" s="3">
-        <v>3606060.703841909</v>
+        <v>3606060.693935043</v>
       </c>
       <c r="P98" s="3">
-        <v>3679648.094685292</v>
+        <v>3679648.085074738</v>
       </c>
       <c r="Q98" s="3">
-        <v>3754688.89560589</v>
+        <v>3754688.886279857</v>
       </c>
       <c r="R98" s="3">
-        <v>43518589.40187588</v>
+        <v>43518589.29251391</v>
       </c>
     </row>
     <row r="99" spans="1:18">
@@ -5841,46 +5845,46 @@
         <v>9862402</v>
       </c>
       <c r="E99" s="3">
-        <v>9882494.170639103</v>
+        <v>9882494.283075074</v>
       </c>
       <c r="F99" s="3">
-        <v>9958388.322736142</v>
+        <v>9958388.526077993</v>
       </c>
       <c r="G99" s="3">
-        <v>10060333.29335512</v>
+        <v>10060333.56856526</v>
       </c>
       <c r="H99" s="3">
-        <v>10184285.89720734</v>
+        <v>10184286.22969356</v>
       </c>
       <c r="I99" s="3">
-        <v>10334521.80854205</v>
+        <v>10334522.18681804</v>
       </c>
       <c r="J99" s="3">
-        <v>10505822.29657672</v>
+        <v>10505822.71159296</v>
       </c>
       <c r="K99" s="3">
-        <v>10683645.12630802</v>
+        <v>10683645.57102295</v>
       </c>
       <c r="L99" s="3">
-        <v>10883459.4837111</v>
+        <v>10883459.95228105</v>
       </c>
       <c r="M99" s="3">
-        <v>11092723.49909816</v>
+        <v>11092723.98702779</v>
       </c>
       <c r="N99" s="3">
-        <v>11308225.89062793</v>
+        <v>11308226.39440787</v>
       </c>
       <c r="O99" s="3">
-        <v>11527855.36709759</v>
+        <v>11527855.88392134</v>
       </c>
       <c r="P99" s="3">
-        <v>11759742.13518353</v>
+        <v>11759742.66270685</v>
       </c>
       <c r="Q99" s="3">
-        <v>11992860.93050711</v>
+        <v>11992861.46700332</v>
       </c>
       <c r="R99" s="3">
-        <v>150036760.2215899</v>
+        <v>150036765.4241941</v>
       </c>
     </row>
     <row r="100" spans="1:18">
@@ -5949,46 +5953,46 @@
         <v>0</v>
       </c>
       <c r="E101" s="3">
-        <v>22116269213.72278</v>
+        <v>22116253715.66332</v>
       </c>
       <c r="F101" s="3">
-        <v>20421012180.5931</v>
+        <v>20420994645.79013</v>
       </c>
       <c r="G101" s="3">
-        <v>20771528543.27423</v>
+        <v>20771509649.63514</v>
       </c>
       <c r="H101" s="3">
-        <v>21159674998.5137</v>
+        <v>21159655108.05441</v>
       </c>
       <c r="I101" s="3">
-        <v>21604488061.23732</v>
+        <v>21604467435.44141</v>
       </c>
       <c r="J101" s="3">
-        <v>22080907360.988</v>
+        <v>22080886163.10287</v>
       </c>
       <c r="K101" s="3">
-        <v>22535279633.2319</v>
+        <v>22535257964.70835</v>
       </c>
       <c r="L101" s="3">
-        <v>23091172233.15044</v>
+        <v>23091150210.64363</v>
       </c>
       <c r="M101" s="3">
-        <v>23617088933.13458</v>
+        <v>23617066601.45523</v>
       </c>
       <c r="N101" s="3">
-        <v>24167415552.43852</v>
+        <v>24167392955.56987</v>
       </c>
       <c r="O101" s="3">
-        <v>24708355906.74166</v>
+        <v>24708333086.26275</v>
       </c>
       <c r="P101" s="3">
-        <v>25306705648.31482</v>
+        <v>25306682647.37967</v>
       </c>
       <c r="Q101" s="3">
-        <v>25870301746.77601</v>
+        <v>25870278572.07784</v>
       </c>
       <c r="R101" s="3">
-        <v>297450200012.1171</v>
+        <v>297449928755.7846</v>
       </c>
     </row>
     <row r="102" spans="1:18">
@@ -6003,46 +6007,46 @@
         <v>0</v>
       </c>
       <c r="E102" s="3">
-        <v>56711451077.44146</v>
+        <v>56710984810.87008</v>
       </c>
       <c r="F102" s="3">
-        <v>56651238498.00659</v>
+        <v>56650690319.25446</v>
       </c>
       <c r="G102" s="3">
-        <v>56537321787.42278</v>
+        <v>56536713572.00832</v>
       </c>
       <c r="H102" s="3">
-        <v>56560300563.5425</v>
+        <v>56559649854.79473</v>
       </c>
       <c r="I102" s="3">
-        <v>56827883202.09897</v>
+        <v>56827201462.59061</v>
       </c>
       <c r="J102" s="3">
-        <v>57337595430.84216</v>
+        <v>57336890657.5496</v>
       </c>
       <c r="K102" s="3">
-        <v>58068857847.76646</v>
+        <v>58068135644.8448</v>
       </c>
       <c r="L102" s="3">
-        <v>58971109840.46515</v>
+        <v>58970374118.81216</v>
       </c>
       <c r="M102" s="3">
-        <v>60004630288.55322</v>
+        <v>60003884151.02452</v>
       </c>
       <c r="N102" s="3">
-        <v>61163056467.04699</v>
+        <v>61162302070.12635</v>
       </c>
       <c r="O102" s="3">
-        <v>62413501656.19044</v>
+        <v>62412740549.30882</v>
       </c>
       <c r="P102" s="3">
-        <v>63724289908.36222</v>
+        <v>63723523361.52563</v>
       </c>
       <c r="Q102" s="3">
-        <v>65089576388.6926</v>
+        <v>65088805475.06082</v>
       </c>
       <c r="R102" s="3">
-        <v>770060812956.4315</v>
+        <v>770051896047.7709</v>
       </c>
     </row>
     <row r="103" spans="1:18">
@@ -6057,46 +6061,46 @@
         <v>0</v>
       </c>
       <c r="E103" s="3">
-        <v>553606290.6108379</v>
+        <v>553608983.4906435</v>
       </c>
       <c r="F103" s="3">
-        <v>556931548.4546191</v>
+        <v>556934243.9927058</v>
       </c>
       <c r="G103" s="3">
-        <v>562701969.0727072</v>
+        <v>562704681.9292293</v>
       </c>
       <c r="H103" s="3">
-        <v>569818361.9014</v>
+        <v>569821086.080349</v>
       </c>
       <c r="I103" s="3">
-        <v>578300950.9083042</v>
+        <v>578303685.2751822</v>
       </c>
       <c r="J103" s="3">
-        <v>588029716.5223192</v>
+        <v>588032459.8571357</v>
       </c>
       <c r="K103" s="3">
-        <v>598213576.2511075</v>
+        <v>598216323.9351237</v>
       </c>
       <c r="L103" s="3">
-        <v>609332555.0452871</v>
+        <v>609335307.9490631</v>
       </c>
       <c r="M103" s="3">
-        <v>621205997.5996865</v>
+        <v>621208755.0826558</v>
       </c>
       <c r="N103" s="3">
-        <v>633375543.9875937</v>
+        <v>633378303.1733822</v>
       </c>
       <c r="O103" s="3">
-        <v>645732977.2324693</v>
+        <v>645735737.1091161</v>
       </c>
       <c r="P103" s="3">
-        <v>658670340.0513846</v>
+        <v>658673101.9670923</v>
       </c>
       <c r="Q103" s="3">
-        <v>671851653.3779866</v>
+        <v>671854416.1225097</v>
       </c>
       <c r="R103" s="3">
-        <v>7847771481.015704</v>
+        <v>7847807085.964189</v>
       </c>
     </row>
     <row r="104" spans="1:18">
@@ -6111,46 +6115,46 @@
         <v>0</v>
       </c>
       <c r="E104" s="3">
-        <v>378068594.8660637</v>
+        <v>378064447.8423566</v>
       </c>
       <c r="F104" s="3">
-        <v>387582786.5729082</v>
+        <v>387578541.0656824</v>
       </c>
       <c r="G104" s="3">
-        <v>394822487.0365984</v>
+        <v>394818208.2182666</v>
       </c>
       <c r="H104" s="3">
-        <v>401777998.4702572</v>
+        <v>401773712.1109512</v>
       </c>
       <c r="I104" s="3">
-        <v>410325629.0069265</v>
+        <v>410321325.5408045</v>
       </c>
       <c r="J104" s="3">
-        <v>419027314.2628838</v>
+        <v>419023003.4331913</v>
       </c>
       <c r="K104" s="3">
-        <v>426125448.5678899</v>
+        <v>426121152.7531943</v>
       </c>
       <c r="L104" s="3">
-        <v>436254480.2999387</v>
+        <v>436250163.6277329</v>
       </c>
       <c r="M104" s="3">
-        <v>445107817.1610646</v>
+        <v>445103504.5253589</v>
       </c>
       <c r="N104" s="3">
-        <v>453791546.9079043</v>
+        <v>453787240.3567241</v>
       </c>
       <c r="O104" s="3">
-        <v>462480690.605985</v>
+        <v>462476388.2690597</v>
       </c>
       <c r="P104" s="3">
-        <v>472762662.1427463</v>
+        <v>472758348.8194222</v>
       </c>
       <c r="Q104" s="3">
-        <v>481608124.954829</v>
+        <v>481603820.9517874</v>
       </c>
       <c r="R104" s="3">
-        <v>5569735580.855995</v>
+        <v>5569679857.514531</v>
       </c>
     </row>
     <row r="105" spans="1:18">
@@ -6327,46 +6331,46 @@
         <v>0</v>
       </c>
       <c r="E108" s="3">
-        <v>79981358765.64481</v>
+        <v>79980879693.89377</v>
       </c>
       <c r="F108" s="3">
-        <v>78246987326.68169</v>
+        <v>78246424308.66469</v>
       </c>
       <c r="G108" s="3">
-        <v>78508785696.4883</v>
+        <v>78508161300.29126</v>
       </c>
       <c r="H108" s="3">
-        <v>78943055440.8481</v>
+        <v>78942387565.82001</v>
       </c>
       <c r="I108" s="3">
-        <v>79680650491.03897</v>
+        <v>79679950860.10156</v>
       </c>
       <c r="J108" s="3">
-        <v>80696573878.44313</v>
+        <v>80695850650.60025</v>
       </c>
       <c r="K108" s="3">
-        <v>81911720531.40306</v>
+        <v>81910979407.64185</v>
       </c>
       <c r="L108" s="3">
-        <v>83398464011.67831</v>
+        <v>83397709020.42229</v>
       </c>
       <c r="M108" s="3">
-        <v>84993103548.14752</v>
+        <v>84992337836.42245</v>
       </c>
       <c r="N108" s="3">
-        <v>86734049277.11188</v>
+        <v>86733275042.50839</v>
       </c>
       <c r="O108" s="3">
-        <v>88557819662.7368</v>
+        <v>88557038495.2529</v>
       </c>
       <c r="P108" s="3">
-        <v>90500716594.61182</v>
+        <v>90499929808.75578</v>
       </c>
       <c r="Q108" s="3">
-        <v>92466012508.03021</v>
+        <v>92465221182.44478</v>
       </c>
       <c r="R108" s="3">
-        <v>1084619297732.865</v>
+        <v>1084610145172.82</v>
       </c>
     </row>
     <row r="109" spans="1:18">
@@ -7892,43 +7896,43 @@
         <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>0.002564401507415981</v>
+        <v>0.002599115169612589</v>
       </c>
       <c r="G29" s="3">
-        <v>0.002469020576582204</v>
+        <v>0.00250244309095996</v>
       </c>
       <c r="H29" s="3">
-        <v>0.002380029527268659</v>
+        <v>0.002412247392056459</v>
       </c>
       <c r="I29" s="3">
-        <v>0.002293127391080968</v>
+        <v>0.002324168883373641</v>
       </c>
       <c r="J29" s="3">
-        <v>0.002209749477033536</v>
+        <v>0.002239662303345267</v>
       </c>
       <c r="K29" s="3">
-        <v>0.002132694579841571</v>
+        <v>0.002161564333271001</v>
       </c>
       <c r="L29" s="3">
-        <v>0.002059163800388244</v>
+        <v>0.002087038186036297</v>
       </c>
       <c r="M29" s="3">
-        <v>0.001986758180905669</v>
+        <v>0.002013652429781619</v>
       </c>
       <c r="N29" s="3">
-        <v>0.001920369915584298</v>
+        <v>0.001946365483107301</v>
       </c>
       <c r="O29" s="3">
-        <v>0.001855723998997609</v>
+        <v>0.00188084447090696</v>
       </c>
       <c r="P29" s="3">
-        <v>0.001793513438897993</v>
+        <v>0.001817791782005706</v>
       </c>
       <c r="Q29" s="3">
-        <v>0.001733807157082225</v>
+        <v>0.001757277271177447</v>
       </c>
       <c r="R29" s="3">
-        <v>0.001677964016230331</v>
+        <v>0.001700678195686643</v>
       </c>
     </row>
     <row r="30" spans="1:18">
@@ -7946,43 +7950,43 @@
         <v>0</v>
       </c>
       <c r="F30" s="3">
-        <v>0.002453949757096566</v>
+        <v>0.002487168261558114</v>
       </c>
       <c r="G30" s="3">
-        <v>0.002362676993695704</v>
+        <v>0.002394659961574044</v>
       </c>
       <c r="H30" s="3">
-        <v>0.002277518892199037</v>
+        <v>0.002308349096143915</v>
       </c>
       <c r="I30" s="3">
-        <v>0.002194359731914558</v>
+        <v>0.002224064231093502</v>
       </c>
       <c r="J30" s="3">
-        <v>0.002114573001430968</v>
+        <v>0.002143197447583205</v>
       </c>
       <c r="K30" s="3">
-        <v>0.002040836948125548</v>
+        <v>0.002068463247755583</v>
       </c>
       <c r="L30" s="3">
-        <v>0.001970473224716091</v>
+        <v>0.001997147028210763</v>
       </c>
       <c r="M30" s="3">
-        <v>0.001901186199331081</v>
+        <v>0.001926922081682411</v>
       </c>
       <c r="N30" s="3">
-        <v>0.001837657353677109</v>
+        <v>0.001862533261924777</v>
       </c>
       <c r="O30" s="3">
-        <v>0.001775795811774866</v>
+        <v>0.00179983431579299</v>
       </c>
       <c r="P30" s="3">
-        <v>0.001716264732728229</v>
+        <v>0.001739497379409955</v>
       </c>
       <c r="Q30" s="3">
-        <v>0.001659130069792166</v>
+        <v>0.001681589298823362</v>
       </c>
       <c r="R30" s="3">
-        <v>0.00160569215785337</v>
+        <v>0.00162742801122823</v>
       </c>
     </row>
     <row r="31" spans="1:18">
@@ -8000,43 +8004,43 @@
         <v>0</v>
       </c>
       <c r="F31" s="3">
-        <v>0.001409166748951964</v>
+        <v>0.001428242286990897</v>
       </c>
       <c r="G31" s="3">
-        <v>0.001406115390351929</v>
+        <v>0.001425149638482397</v>
       </c>
       <c r="H31" s="3">
-        <v>0.001392738326124824</v>
+        <v>0.001411592782809426</v>
       </c>
       <c r="I31" s="3">
-        <v>0.001372021495389217</v>
+        <v>0.001390596232811729</v>
       </c>
       <c r="J31" s="3">
-        <v>0.00134924267826043</v>
+        <v>0.001367509303404355</v>
       </c>
       <c r="K31" s="3">
-        <v>0.001323534836490095</v>
+        <v>0.001341453488126299</v>
       </c>
       <c r="L31" s="3">
-        <v>0.001296812372786222</v>
+        <v>0.001314369240878554</v>
       </c>
       <c r="M31" s="3">
-        <v>0.001272965514029712</v>
+        <v>0.001290199502205158</v>
       </c>
       <c r="N31" s="3">
-        <v>0.001246288885130375</v>
+        <v>0.001263161673635733</v>
       </c>
       <c r="O31" s="3">
-        <v>0.001220630094635923</v>
+        <v>0.001237155467287872</v>
       </c>
       <c r="P31" s="3">
-        <v>0.001196433385872885</v>
+        <v>0.001212631133174352</v>
       </c>
       <c r="Q31" s="3">
-        <v>0.001173395040672774</v>
+        <v>0.001189280847891403</v>
       </c>
       <c r="R31" s="3">
-        <v>0.001149193098021512</v>
+        <v>0.001164751215275217</v>
       </c>
     </row>
     <row r="32" spans="1:18">
@@ -8054,43 +8058,43 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>0.0002500604389138322</v>
+        <v>0.0002534454445691819</v>
       </c>
       <c r="G32" s="3">
-        <v>0.0002469743901939634</v>
+        <v>0.0002503176232715547</v>
       </c>
       <c r="H32" s="3">
-        <v>0.0002458220852626858</v>
+        <v>0.000249149902651928</v>
       </c>
       <c r="I32" s="3">
-        <v>0.0002424403259527239</v>
+        <v>0.000245722532542103</v>
       </c>
       <c r="J32" s="3">
-        <v>0.0002384827857893815</v>
+        <v>0.0002417114815791392</v>
       </c>
       <c r="K32" s="3">
-        <v>0.0002341043661624131</v>
+        <v>0.0002372738037682449</v>
       </c>
       <c r="L32" s="3">
-        <v>0.0002294340862124019</v>
+        <v>0.0002325402965454196</v>
       </c>
       <c r="M32" s="3">
-        <v>0.0002250779721950596</v>
+        <v>0.0002281252022227355</v>
       </c>
       <c r="N32" s="3">
-        <v>0.0002205633557193276</v>
+        <v>0.0002235494573745129</v>
       </c>
       <c r="O32" s="3">
-        <v>0.0002159698563981106</v>
+        <v>0.0002188937619583986</v>
       </c>
       <c r="P32" s="3">
-        <v>0.000211645449134693</v>
+        <v>0.0002145108014019884</v>
       </c>
       <c r="Q32" s="3">
-        <v>0.0002075434226265472</v>
+        <v>0.000210353232500083</v>
       </c>
       <c r="R32" s="3">
-        <v>0.0002033581938272363</v>
+        <v>0.000206111335538163</v>
       </c>
     </row>
     <row r="33" spans="1:18">
@@ -8108,43 +8112,43 @@
         <v>0.3538</v>
       </c>
       <c r="F33" s="3">
-        <v>0.7610267205170879</v>
+        <v>0.7608896170269077</v>
       </c>
       <c r="G33" s="3">
-        <v>0.7468680838563049</v>
+        <v>0.7467335311287328</v>
       </c>
       <c r="H33" s="3">
-        <v>0.7298938092232071</v>
+        <v>0.7297623145121707</v>
       </c>
       <c r="I33" s="3">
-        <v>0.7168599912013642</v>
+        <v>0.7167308446101678</v>
       </c>
       <c r="J33" s="3">
-        <v>0.7042835001276558</v>
+        <v>0.7041566192661295</v>
       </c>
       <c r="K33" s="3">
-        <v>0.6891701202965903</v>
+        <v>0.6890459622003328</v>
       </c>
       <c r="L33" s="3">
-        <v>0.6746917564248134</v>
+        <v>0.6745702066919226</v>
       </c>
       <c r="M33" s="3">
-        <v>0.663539826566552</v>
+        <v>0.6634202859201552</v>
       </c>
       <c r="N33" s="3">
-        <v>0.6474864436657483</v>
+        <v>0.6473697951317643</v>
       </c>
       <c r="O33" s="3">
-        <v>0.6346902688897453</v>
+        <v>0.6345759256627571</v>
       </c>
       <c r="P33" s="3">
-        <v>0.6223900698802541</v>
+        <v>0.6222779426072774</v>
       </c>
       <c r="Q33" s="3">
-        <v>0.6105575590460286</v>
+        <v>0.6104475634702566</v>
       </c>
       <c r="R33" s="3">
-        <v>0.5969391748293885</v>
+        <v>0.5968316326865335</v>
       </c>
     </row>
     <row r="34" spans="1:18">
@@ -8162,43 +8166,43 @@
         <v>0.1</v>
       </c>
       <c r="F34" s="3">
-        <v>0.0002576823241363665</v>
+        <v>0.0002611705053467731</v>
       </c>
       <c r="G34" s="3">
-        <v>0.0002562786455172604</v>
+        <v>0.0002597478261765474</v>
       </c>
       <c r="H34" s="3">
-        <v>0.0002549746638582288</v>
+        <v>0.0002584262645730753</v>
       </c>
       <c r="I34" s="3">
-        <v>0.0002527835331190223</v>
+        <v>0.000256205575093043</v>
       </c>
       <c r="J34" s="3">
-        <v>0.0002499846631714428</v>
+        <v>0.0002533688996642563</v>
       </c>
       <c r="K34" s="3">
-        <v>0.0002466335505493132</v>
+        <v>0.0002499724815757804</v>
       </c>
       <c r="L34" s="3">
-        <v>0.0002428079555042368</v>
+        <v>0.0002460951373487515</v>
       </c>
       <c r="M34" s="3">
-        <v>0.0002388045912143011</v>
+        <v>0.0002420376016495614</v>
       </c>
       <c r="N34" s="3">
-        <v>0.0002345932659817693</v>
+        <v>0.0002377692783238255</v>
       </c>
       <c r="O34" s="3">
-        <v>0.0002302093520999083</v>
+        <v>0.0002333260222149338</v>
       </c>
       <c r="P34" s="3">
-        <v>0.0002258316467268621</v>
+        <v>0.000228889053272903</v>
       </c>
       <c r="Q34" s="3">
-        <v>0.0002215239390208492</v>
+        <v>0.0002245230260540979</v>
       </c>
       <c r="R34" s="3">
-        <v>0.0002172123793429828</v>
+        <v>0.0002201530924998509</v>
       </c>
     </row>
     <row r="35" spans="1:18">
@@ -8216,43 +8220,43 @@
         <v>0</v>
       </c>
       <c r="F35" s="3">
-        <v>0.0002604796238685752</v>
+        <v>0.0002640056714262311</v>
       </c>
       <c r="G35" s="3">
-        <v>0.0002572649897853785</v>
+        <v>0.0002607475242412028</v>
       </c>
       <c r="H35" s="3">
-        <v>0.0002560646721486311</v>
+        <v>0.0002595311485957583</v>
       </c>
       <c r="I35" s="3">
-        <v>0.000252542006200754</v>
+        <v>0.000255960971398024</v>
       </c>
       <c r="J35" s="3">
-        <v>0.0002484195685306058</v>
+        <v>0.0002517827933116033</v>
       </c>
       <c r="K35" s="3">
-        <v>0.0002438587147525136</v>
+        <v>0.0002471602122585884</v>
       </c>
       <c r="L35" s="3">
-        <v>0.0002389938398045852</v>
+        <v>0.0002422294755681454</v>
       </c>
       <c r="M35" s="3">
-        <v>0.0002344562210365204</v>
+        <v>0.0002376304189820161</v>
       </c>
       <c r="N35" s="3">
-        <v>0.0002297534955409663</v>
+        <v>0.000232864018098451</v>
       </c>
       <c r="O35" s="3">
-        <v>0.0002249686004146986</v>
+        <v>0.0002280143353733318</v>
       </c>
       <c r="P35" s="3">
-        <v>0.0002204640095153052</v>
+        <v>0.0002234487514604046</v>
       </c>
       <c r="Q35" s="3">
-        <v>0.0002161910652359867</v>
+        <v>0.0002191179505209198</v>
       </c>
       <c r="R35" s="3">
-        <v>0.0002118314519033711</v>
+        <v>0.0002146993078522531</v>
       </c>
     </row>
     <row r="36" spans="1:18">
@@ -8270,43 +8274,43 @@
         <v>0</v>
       </c>
       <c r="F36" s="3">
-        <v>0.001452863353095384</v>
+        <v>0.001472530401142008</v>
       </c>
       <c r="G36" s="3">
-        <v>0.001450424043167817</v>
+        <v>0.001470058076621723</v>
       </c>
       <c r="H36" s="3">
-        <v>0.001440642040145013</v>
+        <v>0.001460144252240262</v>
       </c>
       <c r="I36" s="3">
-        <v>0.001427027984835676</v>
+        <v>0.001446346441245561</v>
       </c>
       <c r="J36" s="3">
-        <v>0.001410416772727882</v>
+        <v>0.001429510782161394</v>
       </c>
       <c r="K36" s="3">
-        <v>0.00139054243586183</v>
+        <v>0.001409367699587112</v>
       </c>
       <c r="L36" s="3">
-        <v>0.001368295620595167</v>
+        <v>0.001386819915889749</v>
       </c>
       <c r="M36" s="3">
-        <v>0.001345709005383079</v>
+        <v>0.001363927651304483</v>
       </c>
       <c r="N36" s="3">
-        <v>0.001321266801314558</v>
+        <v>0.001339154618990581</v>
       </c>
       <c r="O36" s="3">
-        <v>0.001296424470407839</v>
+        <v>0.001313976004988089</v>
       </c>
       <c r="P36" s="3">
-        <v>0.001271747039237526</v>
+        <v>0.001288964494472052</v>
       </c>
       <c r="Q36" s="3">
-        <v>0.001247512579931104</v>
+        <v>0.001264401935492678</v>
       </c>
       <c r="R36" s="3">
-        <v>0.001222955811912202</v>
+        <v>0.001239512693220415</v>
       </c>
     </row>
     <row r="37" spans="1:18">
@@ -8327,40 +8331,40 @@
         <v>0.95</v>
       </c>
       <c r="G37" s="3">
-        <v>0.9448250440047834</v>
+        <v>0.944825046534562</v>
       </c>
       <c r="H37" s="3">
-        <v>0.9400176417887725</v>
+        <v>0.940017905231866</v>
       </c>
       <c r="I37" s="3">
-        <v>0.9319395781915791</v>
+        <v>0.9319402128322991</v>
       </c>
       <c r="J37" s="3">
-        <v>0.9216209563803546</v>
+        <v>0.9216218897361698</v>
       </c>
       <c r="K37" s="3">
-        <v>0.9092663759810471</v>
+        <v>0.9092675192464091</v>
       </c>
       <c r="L37" s="3">
-        <v>0.8951625164904783</v>
+        <v>0.8951637941309457</v>
       </c>
       <c r="M37" s="3">
-        <v>0.8804032733480335</v>
+        <v>0.8804046278571261</v>
       </c>
       <c r="N37" s="3">
-        <v>0.864877338519892</v>
+        <v>0.8648787278169774</v>
       </c>
       <c r="O37" s="3">
-        <v>0.8487151193931972</v>
+        <v>0.8487165149444234</v>
       </c>
       <c r="P37" s="3">
-        <v>0.8325757892380058</v>
+        <v>0.8325771714556455</v>
       </c>
       <c r="Q37" s="3">
-        <v>0.816694520181512</v>
+        <v>0.8166958763899654</v>
       </c>
       <c r="R37" s="3">
-        <v>0.8007990500218846</v>
+        <v>0.8008003721444821</v>
       </c>
     </row>
     <row r="38" spans="1:18">
@@ -8378,43 +8382,43 @@
         <v>0</v>
       </c>
       <c r="F38" s="3">
-        <v>0.001198222807234105</v>
+        <v>0.001214442849862495</v>
       </c>
       <c r="G38" s="3">
-        <v>0.001191695701655261</v>
+        <v>0.001207827391720945</v>
       </c>
       <c r="H38" s="3">
-        <v>0.001185632186940764</v>
+        <v>0.0012016821302648</v>
       </c>
       <c r="I38" s="3">
-        <v>0.001175443429003454</v>
+        <v>0.00119135592418265</v>
       </c>
       <c r="J38" s="3">
-        <v>0.001162428683747209</v>
+        <v>0.001178165383438792</v>
       </c>
       <c r="K38" s="3">
-        <v>0.001146846010054306</v>
+        <v>0.001162372039327379</v>
       </c>
       <c r="L38" s="3">
-        <v>0.001129056993094701</v>
+        <v>0.001144342388671694</v>
       </c>
       <c r="M38" s="3">
-        <v>0.001110441349146501</v>
+        <v>0.001125474847670461</v>
       </c>
       <c r="N38" s="3">
-        <v>0.001090858686815227</v>
+        <v>0.001105627144205789</v>
       </c>
       <c r="O38" s="3">
-        <v>0.001070473487264574</v>
+        <v>0.001084966003299443</v>
       </c>
       <c r="P38" s="3">
-        <v>0.001050117157279909</v>
+        <v>0.001064334097718999</v>
       </c>
       <c r="Q38" s="3">
-        <v>0.001030086316446949</v>
+        <v>0.001044032071151556</v>
       </c>
       <c r="R38" s="3">
-        <v>0.00101003756394487</v>
+        <v>0.001023711880124307</v>
       </c>
     </row>
     <row r="39" spans="1:18">
@@ -8432,43 +8436,43 @@
         <v>0</v>
       </c>
       <c r="F39" s="3">
-        <v>0.00425386194800057</v>
+        <v>0.004311445413876276</v>
       </c>
       <c r="G39" s="3">
-        <v>0.00417472033036335</v>
+        <v>0.004231232475943694</v>
       </c>
       <c r="H39" s="3">
-        <v>0.004079840322855092</v>
+        <v>0.004135068101490428</v>
       </c>
       <c r="I39" s="3">
-        <v>0.004006986031375538</v>
+        <v>0.0040612275996781</v>
       </c>
       <c r="J39" s="3">
-        <v>0.003936688030825089</v>
+        <v>0.003989977992666202</v>
       </c>
       <c r="K39" s="3">
-        <v>0.003852209746901804</v>
+        <v>0.003904356147330018</v>
       </c>
       <c r="L39" s="3">
-        <v>0.003771280970706388</v>
+        <v>0.003822331858520565</v>
       </c>
       <c r="M39" s="3">
-        <v>0.003708945748050084</v>
+        <v>0.003759152819536754</v>
       </c>
       <c r="N39" s="3">
-        <v>0.003619213189629517</v>
+        <v>0.0036682055739028</v>
       </c>
       <c r="O39" s="3">
-        <v>0.003547687237265298</v>
+        <v>0.003595711392600373</v>
       </c>
       <c r="P39" s="3">
-        <v>0.003478933608636125</v>
+        <v>0.003526027063286413</v>
       </c>
       <c r="Q39" s="3">
-        <v>0.003412794186418708</v>
+        <v>0.003458992328242943</v>
       </c>
       <c r="R39" s="3">
-        <v>0.003336672383004164</v>
+        <v>0.003381840083003324</v>
       </c>
     </row>
     <row r="40" spans="1:18">
@@ -8650,43 +8654,43 @@
         <v>0</v>
       </c>
       <c r="F43" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="G43" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="H43" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="I43" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="J43" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="K43" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="L43" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="M43" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="N43" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="O43" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="P43" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="Q43" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="R43" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
     </row>
     <row r="44" spans="1:18">
@@ -8704,43 +8708,43 @@
         <v>0</v>
       </c>
       <c r="F44" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="G44" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="H44" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="I44" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="J44" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="K44" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="L44" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="M44" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="N44" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="O44" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="P44" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="Q44" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="R44" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
     </row>
     <row r="45" spans="1:18">
@@ -8758,43 +8762,43 @@
         <v>0</v>
       </c>
       <c r="F45" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="G45" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="H45" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="I45" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="J45" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="K45" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="L45" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="M45" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="N45" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="O45" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="P45" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="Q45" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="R45" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
     </row>
     <row r="46" spans="1:18">
@@ -8812,43 +8816,43 @@
         <v>0</v>
       </c>
       <c r="F46" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="G46" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="H46" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="I46" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="J46" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="K46" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="L46" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="M46" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="N46" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="O46" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="P46" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="Q46" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="R46" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
     </row>
     <row r="47" spans="1:18">
@@ -8866,43 +8870,43 @@
         <v>3317810.965630114</v>
       </c>
       <c r="F47" s="3">
-        <v>7136638.774644202</v>
+        <v>7135353.066721234</v>
       </c>
       <c r="G47" s="3">
-        <v>7136638.774644202</v>
+        <v>7135353.066721234</v>
       </c>
       <c r="H47" s="3">
-        <v>7136638.774644202</v>
+        <v>7135353.066721234</v>
       </c>
       <c r="I47" s="3">
-        <v>7136638.774644202</v>
+        <v>7135353.066721234</v>
       </c>
       <c r="J47" s="3">
-        <v>7136638.774644202</v>
+        <v>7135353.066721234</v>
       </c>
       <c r="K47" s="3">
-        <v>7136638.774644202</v>
+        <v>7135353.066721234</v>
       </c>
       <c r="L47" s="3">
-        <v>7136638.774644202</v>
+        <v>7135353.066721234</v>
       </c>
       <c r="M47" s="3">
-        <v>7136638.774644202</v>
+        <v>7135353.066721234</v>
       </c>
       <c r="N47" s="3">
-        <v>7136638.774644202</v>
+        <v>7135353.066721234</v>
       </c>
       <c r="O47" s="3">
-        <v>7136638.774644202</v>
+        <v>7135353.066721234</v>
       </c>
       <c r="P47" s="3">
-        <v>7136638.774644202</v>
+        <v>7135353.066721234</v>
       </c>
       <c r="Q47" s="3">
-        <v>7136638.774644202</v>
+        <v>7135353.066721234</v>
       </c>
       <c r="R47" s="3">
-        <v>7136638.774644202</v>
+        <v>7135353.066721234</v>
       </c>
     </row>
     <row r="48" spans="1:18">
@@ -8920,43 +8924,43 @@
         <v>4095441.930000001</v>
       </c>
       <c r="F48" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="G48" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="H48" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="I48" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="J48" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="K48" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="L48" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="M48" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="N48" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="O48" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="P48" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="Q48" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="R48" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
     </row>
     <row r="49" spans="1:18">
@@ -8974,43 +8978,43 @@
         <v>0</v>
       </c>
       <c r="F49" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="G49" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="H49" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="I49" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="J49" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="K49" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="L49" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="M49" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="N49" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="O49" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="P49" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="Q49" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="R49" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
     </row>
     <row r="50" spans="1:18">
@@ -9028,43 +9032,43 @@
         <v>0</v>
       </c>
       <c r="F50" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="G50" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="H50" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="I50" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="J50" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="K50" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="L50" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="M50" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="N50" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="O50" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="P50" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="Q50" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="R50" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
     </row>
     <row r="51" spans="1:18">
@@ -9136,43 +9140,43 @@
         <v>0</v>
       </c>
       <c r="F52" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="G52" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="H52" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="I52" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="J52" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="K52" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="L52" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="M52" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="N52" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="O52" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="P52" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="Q52" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="R52" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
     </row>
     <row r="53" spans="1:18">
@@ -9190,43 +9194,43 @@
         <v>0</v>
       </c>
       <c r="F53" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="G53" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="H53" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="I53" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="J53" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="K53" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="L53" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="M53" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="N53" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="O53" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="P53" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="Q53" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
       <c r="R53" s="3">
-        <v>10553.22994887927</v>
+        <v>10696.08638476464</v>
       </c>
     </row>
     <row r="54" spans="1:18">
@@ -9424,43 +9428,43 @@
         <v>0</v>
       </c>
       <c r="F58" s="3">
-        <v>0.05066587387301576</v>
+        <v>0.05052450348137158</v>
       </c>
       <c r="G58" s="3">
-        <v>0.04878139587784234</v>
+        <v>0.04864528364858356</v>
       </c>
       <c r="H58" s="3">
-        <v>0.04702316524691019</v>
+        <v>0.04689195891848554</v>
       </c>
       <c r="I58" s="3">
-        <v>0.04530620608172162</v>
+        <v>0.04517979049647507</v>
       </c>
       <c r="J58" s="3">
-        <v>0.0436588763384245</v>
+        <v>0.04353705721294811</v>
       </c>
       <c r="K58" s="3">
-        <v>0.04213647288828762</v>
+        <v>0.04201890164714706</v>
       </c>
       <c r="L58" s="3">
-        <v>0.04068369679733889</v>
+        <v>0.04057017916288167</v>
       </c>
       <c r="M58" s="3">
-        <v>0.03925315092774991</v>
+        <v>0.03914362487212849</v>
       </c>
       <c r="N58" s="3">
-        <v>0.03794149225507573</v>
+        <v>0.03783562605343658</v>
       </c>
       <c r="O58" s="3">
-        <v>0.03666425784123113</v>
+        <v>0.0365619554413288</v>
       </c>
       <c r="P58" s="3">
-        <v>0.03543513970880854</v>
+        <v>0.03533626685424857</v>
       </c>
       <c r="Q58" s="3">
-        <v>0.03425549957244289</v>
+        <v>0.03415991820730823</v>
       </c>
       <c r="R58" s="3">
-        <v>0.03315218500844309</v>
+        <v>0.03305968216540026</v>
       </c>
     </row>
     <row r="59" spans="1:18">
@@ -9478,43 +9482,43 @@
         <v>0</v>
       </c>
       <c r="F59" s="3">
-        <v>0.04848363585975853</v>
+        <v>0.04834835445502037</v>
       </c>
       <c r="G59" s="3">
-        <v>0.04668032451980794</v>
+        <v>0.04655007480229627</v>
       </c>
       <c r="H59" s="3">
-        <v>0.04499782292354141</v>
+        <v>0.04487226780401894</v>
       </c>
       <c r="I59" s="3">
-        <v>0.04335481518307068</v>
+        <v>0.04323384446385536</v>
       </c>
       <c r="J59" s="3">
-        <v>0.04177843784444742</v>
+        <v>0.04166186561014323</v>
       </c>
       <c r="K59" s="3">
-        <v>0.04032160607849246</v>
+        <v>0.04020909876721376</v>
       </c>
       <c r="L59" s="3">
-        <v>0.03893140274052467</v>
+        <v>0.03882277444238302</v>
       </c>
       <c r="M59" s="3">
-        <v>0.03756247214247229</v>
+        <v>0.03745766350123156</v>
       </c>
       <c r="N59" s="3">
-        <v>0.03630730813172978</v>
+        <v>0.03620600171031103</v>
       </c>
       <c r="O59" s="3">
-        <v>0.0350850856870208</v>
+        <v>0.03498718957026033</v>
       </c>
       <c r="P59" s="3">
-        <v>0.03390890709962764</v>
+        <v>0.03381429281370977</v>
       </c>
       <c r="Q59" s="3">
-        <v>0.0327800754335549</v>
+        <v>0.03268861086879121</v>
       </c>
       <c r="R59" s="3">
-        <v>0.03172428190882851</v>
+        <v>0.03163576327063582</v>
       </c>
     </row>
     <row r="60" spans="1:18">
@@ -9532,43 +9536,43 @@
         <v>0</v>
       </c>
       <c r="F60" s="3">
-        <v>0.02784145328333968</v>
+        <v>0.02776376870289657</v>
       </c>
       <c r="G60" s="3">
-        <v>0.02777970702130857</v>
+        <v>0.02770219480892229</v>
       </c>
       <c r="H60" s="3">
-        <v>0.02748036185824312</v>
+        <v>0.02740368497822549</v>
       </c>
       <c r="I60" s="3">
-        <v>0.02705166521476859</v>
+        <v>0.02697618454216549</v>
       </c>
       <c r="J60" s="3">
-        <v>0.02659521196356032</v>
+        <v>0.02652100491711657</v>
       </c>
       <c r="K60" s="3">
-        <v>0.02608659893424279</v>
+        <v>0.02601381104076027</v>
       </c>
       <c r="L60" s="3">
-        <v>0.02555996992979412</v>
+        <v>0.02548865145397695</v>
       </c>
       <c r="M60" s="3">
-        <v>0.02509076168474538</v>
+        <v>0.02502075240732942</v>
       </c>
       <c r="N60" s="3">
-        <v>0.02456602440117397</v>
+        <v>0.02449747926203111</v>
       </c>
       <c r="O60" s="3">
-        <v>0.02406124498836237</v>
+        <v>0.02399410830035424</v>
       </c>
       <c r="P60" s="3">
-        <v>0.02358538561402447</v>
+        <v>0.02351957668348375</v>
       </c>
       <c r="Q60" s="3">
-        <v>0.02313228253450909</v>
+        <v>0.02306773786645206</v>
       </c>
       <c r="R60" s="3">
-        <v>0.0226561534621589</v>
+        <v>0.02259293730540348</v>
       </c>
     </row>
     <row r="61" spans="1:18">
@@ -9586,43 +9590,43 @@
         <v>0</v>
       </c>
       <c r="F61" s="3">
-        <v>0.004940540949613477</v>
+        <v>0.004926755611365262</v>
       </c>
       <c r="G61" s="3">
-        <v>0.004879274594297419</v>
+        <v>0.004865660197580111</v>
       </c>
       <c r="H61" s="3">
-        <v>0.004851501278630444</v>
+        <v>0.004837964395168547</v>
       </c>
       <c r="I61" s="3">
-        <v>0.004780176492938474</v>
+        <v>0.004766838632692572</v>
       </c>
       <c r="J61" s="3">
-        <v>0.004700338612199526</v>
+        <v>0.004687223522189627</v>
       </c>
       <c r="K61" s="3">
-        <v>0.00461353439668921</v>
+        <v>0.004600661511982991</v>
       </c>
       <c r="L61" s="3">
-        <v>0.004521455618182165</v>
+        <v>0.004508839655124313</v>
       </c>
       <c r="M61" s="3">
-        <v>0.00443573982283806</v>
+        <v>0.004423363026817353</v>
       </c>
       <c r="N61" s="3">
-        <v>0.0043469592864277</v>
+        <v>0.004334830208881933</v>
       </c>
       <c r="O61" s="3">
-        <v>0.004256617912761481</v>
+        <v>0.004244740908851334</v>
       </c>
       <c r="P61" s="3">
-        <v>0.004171587945647851</v>
+        <v>0.004159948195296616</v>
       </c>
       <c r="Q61" s="3">
-        <v>0.004090935504137328</v>
+        <v>0.004079520793085067</v>
       </c>
       <c r="R61" s="3">
-        <v>0.004008625511764091</v>
+        <v>0.003997440465119703</v>
       </c>
     </row>
     <row r="62" spans="1:18">
@@ -9694,43 +9698,43 @@
         <v>0.1</v>
       </c>
       <c r="F63" s="3">
-        <v>0.005091129488203385</v>
+        <v>0.00507692397047241</v>
       </c>
       <c r="G63" s="3">
-        <v>0.005063146277031989</v>
+        <v>0.005049018766158105</v>
       </c>
       <c r="H63" s="3">
-        <v>0.005035258351269824</v>
+        <v>0.005021208603532402</v>
       </c>
       <c r="I63" s="3">
-        <v>0.004989077144515413</v>
+        <v>0.004975156216181192</v>
       </c>
       <c r="J63" s="3">
-        <v>0.004931468250007467</v>
+        <v>0.004917708037512796</v>
       </c>
       <c r="K63" s="3">
-        <v>0.004863639934118104</v>
+        <v>0.004850068960528428</v>
       </c>
       <c r="L63" s="3">
-        <v>0.004787022218194431</v>
+        <v>0.00477366501483986</v>
       </c>
       <c r="M63" s="3">
-        <v>0.00470733609447494</v>
+        <v>0.004694201227875877</v>
       </c>
       <c r="N63" s="3">
-        <v>0.00462386655038279</v>
+        <v>0.004610964581203205</v>
       </c>
       <c r="O63" s="3">
-        <v>0.004537208560441587</v>
+        <v>0.004524548388320592</v>
       </c>
       <c r="P63" s="3">
-        <v>0.004450824757415112</v>
+        <v>0.004438405619341257</v>
       </c>
       <c r="Q63" s="3">
-        <v>0.004365922046658236</v>
+        <v>0.004353739811420646</v>
       </c>
       <c r="R63" s="3">
-        <v>0.004281006499576523</v>
+        <v>0.004269061204188631</v>
       </c>
     </row>
     <row r="64" spans="1:18">
@@ -9748,43 +9752,43 @@
         <v>0</v>
       </c>
       <c r="F64" s="3">
-        <v>0.005146396822514039</v>
+        <v>0.005132037095172148</v>
       </c>
       <c r="G64" s="3">
-        <v>0.005082577702393144</v>
+        <v>0.005068396039145949</v>
       </c>
       <c r="H64" s="3">
-        <v>0.005053647165240046</v>
+        <v>0.005039546244967236</v>
       </c>
       <c r="I64" s="3">
-        <v>0.004979350513477577</v>
+        <v>0.004965456909054762</v>
       </c>
       <c r="J64" s="3">
-        <v>0.004896186054374506</v>
+        <v>0.004882524502280861</v>
       </c>
       <c r="K64" s="3">
-        <v>0.00480576499655126</v>
+        <v>0.00479235574164895</v>
       </c>
       <c r="L64" s="3">
-        <v>0.004709849602273088</v>
+        <v>0.004696707974087826</v>
       </c>
       <c r="M64" s="3">
-        <v>0.004620562315456312</v>
+        <v>0.004607669819601408</v>
       </c>
       <c r="N64" s="3">
-        <v>0.004528082590028854</v>
+        <v>0.004515448134252013</v>
       </c>
       <c r="O64" s="3">
-        <v>0.004433976992459876</v>
+        <v>0.004421605113386806</v>
       </c>
       <c r="P64" s="3">
-        <v>0.004345404110049845</v>
+        <v>0.004333279370100642</v>
       </c>
       <c r="Q64" s="3">
-        <v>0.00426139115014305</v>
+        <v>0.004249500826130278</v>
       </c>
       <c r="R64" s="3">
-        <v>0.004175651574754261</v>
+        <v>0.004164000484499691</v>
       </c>
     </row>
     <row r="65" spans="1:18">
@@ -9802,43 +9806,43 @@
         <v>0</v>
       </c>
       <c r="F65" s="3">
-        <v>0.02870478401677093</v>
+        <v>0.02862469052882116</v>
       </c>
       <c r="G65" s="3">
-        <v>0.0286552073323771</v>
+        <v>0.0285752518445976</v>
       </c>
       <c r="H65" s="3">
-        <v>0.02844494089718409</v>
+        <v>0.02836557184611204</v>
       </c>
       <c r="I65" s="3">
-        <v>0.02816085168287105</v>
+        <v>0.02808227511869905</v>
       </c>
       <c r="J65" s="3">
-        <v>0.02782098333988842</v>
+        <v>0.02774335495272391</v>
       </c>
       <c r="K65" s="3">
-        <v>0.02742022912906224</v>
+        <v>0.02734371884876183</v>
       </c>
       <c r="L65" s="3">
-        <v>0.02697561573258236</v>
+        <v>0.02690034597118604</v>
       </c>
       <c r="M65" s="3">
-        <v>0.02652656294905238</v>
+        <v>0.02645254611743918</v>
       </c>
       <c r="N65" s="3">
-        <v>0.02604254537902122</v>
+        <v>0.02596987905938967</v>
       </c>
       <c r="O65" s="3">
-        <v>0.02555170629410086</v>
+        <v>0.02548040953484245</v>
       </c>
       <c r="P65" s="3">
-        <v>0.02506492378156634</v>
+        <v>0.02499498527401229</v>
       </c>
       <c r="Q65" s="3">
-        <v>0.02458736541485063</v>
+        <v>0.02451875942849734</v>
       </c>
       <c r="R65" s="3">
-        <v>0.0241037703059678</v>
+        <v>0.02403651369161707</v>
       </c>
     </row>
     <row r="66" spans="1:18">
@@ -9859,40 +9863,40 @@
         <v>0.95</v>
       </c>
       <c r="G66" s="3">
-        <v>0.9447783589723214</v>
+        <v>0.9447783452632396</v>
       </c>
       <c r="H66" s="3">
-        <v>0.9395744981128707</v>
+        <v>0.9395744748393223</v>
       </c>
       <c r="I66" s="3">
-        <v>0.9309571281327228</v>
+        <v>0.930957097813765</v>
       </c>
       <c r="J66" s="3">
-        <v>0.9202073623077993</v>
+        <v>0.9202073268791616</v>
       </c>
       <c r="K66" s="3">
-        <v>0.9075506620128644</v>
+        <v>0.9075506230346938</v>
       </c>
       <c r="L66" s="3">
-        <v>0.8932538678935747</v>
+        <v>0.8932538266228723</v>
       </c>
       <c r="M66" s="3">
-        <v>0.8783845117499283</v>
+        <v>0.8783844691034689</v>
       </c>
       <c r="N66" s="3">
-        <v>0.8628091729039455</v>
+        <v>0.8628091296264666</v>
       </c>
       <c r="O66" s="3">
-        <v>0.8466388730451623</v>
+        <v>0.8466388297133789</v>
       </c>
       <c r="P66" s="3">
-        <v>0.830519736208179</v>
+        <v>0.8305196932034908</v>
       </c>
       <c r="Q66" s="3">
-        <v>0.8146769698032145</v>
+        <v>0.8146769273885249</v>
       </c>
       <c r="R66" s="3">
-        <v>0.7988318081520432</v>
+        <v>0.7988317665513166</v>
       </c>
     </row>
     <row r="67" spans="1:18">
@@ -9910,43 +9914,43 @@
         <v>0</v>
       </c>
       <c r="F67" s="3">
-        <v>0.8307695687276108</v>
+        <v>0.8312980139872032</v>
       </c>
       <c r="G67" s="3">
-        <v>0.8262032735017003</v>
+        <v>0.8267288021846813</v>
       </c>
       <c r="H67" s="3">
-        <v>0.8216525269312537</v>
+        <v>0.8221751525547347</v>
       </c>
       <c r="I67" s="3">
-        <v>0.8141166861502286</v>
+        <v>0.8146345121261824</v>
       </c>
       <c r="J67" s="3">
-        <v>0.8047160773941292</v>
+        <v>0.8052279192538107</v>
       </c>
       <c r="K67" s="3">
-        <v>0.7936478653461948</v>
+        <v>0.7941526637069367</v>
       </c>
       <c r="L67" s="3">
-        <v>0.7811454006254898</v>
+        <v>0.7816422442716456</v>
       </c>
       <c r="M67" s="3">
-        <v>0.7681422336878957</v>
+        <v>0.7686308049293868</v>
       </c>
       <c r="N67" s="3">
-        <v>0.7545216889133025</v>
+        <v>0.7550015956931674</v>
       </c>
       <c r="O67" s="3">
-        <v>0.7403808541344841</v>
+        <v>0.7408517660054545</v>
       </c>
       <c r="P67" s="3">
-        <v>0.7262847611257242</v>
+        <v>0.7267467068813929</v>
       </c>
       <c r="Q67" s="3">
-        <v>0.7124303524797192</v>
+        <v>0.7128834860834502</v>
       </c>
       <c r="R67" s="3">
-        <v>0.6985738492046005</v>
+        <v>0.6990181695199985</v>
       </c>
     </row>
     <row r="68" spans="1:18">
@@ -9964,43 +9968,43 @@
         <v>0</v>
       </c>
       <c r="F68" s="3">
-        <v>0.08404519819043174</v>
+        <v>0.08381069118056998</v>
       </c>
       <c r="G68" s="3">
-        <v>0.08248156659619114</v>
+        <v>0.08225142250744311</v>
       </c>
       <c r="H68" s="3">
-        <v>0.08060698553718681</v>
+        <v>0.08038207199591031</v>
       </c>
       <c r="I68" s="3">
-        <v>0.07916757508116563</v>
+        <v>0.07894667785312622</v>
       </c>
       <c r="J68" s="3">
-        <v>0.07777867025518025</v>
+        <v>0.07756164841710643</v>
       </c>
       <c r="K68" s="3">
-        <v>0.07610960007803046</v>
+        <v>0.07589723536094535</v>
       </c>
       <c r="L68" s="3">
-        <v>0.07451065889992059</v>
+        <v>0.07430275562647172</v>
       </c>
       <c r="M68" s="3">
-        <v>0.07327907776107892</v>
+        <v>0.07307461090537301</v>
       </c>
       <c r="N68" s="3">
-        <v>0.07150619684750444</v>
+        <v>0.0713066767705656</v>
       </c>
       <c r="O68" s="3">
-        <v>0.07009303090190158</v>
+        <v>0.06989745390948723</v>
       </c>
       <c r="P68" s="3">
-        <v>0.0687346388301593</v>
+        <v>0.06854285208953594</v>
       </c>
       <c r="Q68" s="3">
-        <v>0.06742789664707639</v>
+        <v>0.06723975604220632</v>
       </c>
       <c r="R68" s="3">
-        <v>0.06592392869212303</v>
+        <v>0.06573998453197125</v>
       </c>
     </row>
     <row r="69" spans="1:18">
@@ -10182,43 +10186,43 @@
         <v>0</v>
       </c>
       <c r="F72" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="G72" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="H72" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="I72" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="J72" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="K72" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="L72" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="M72" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="N72" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="O72" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="P72" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="Q72" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="R72" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
     </row>
     <row r="73" spans="1:18">
@@ -10236,43 +10240,43 @@
         <v>0</v>
       </c>
       <c r="F73" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="G73" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="H73" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="I73" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="J73" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="K73" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="L73" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="M73" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="N73" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="O73" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="P73" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="Q73" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="R73" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
     </row>
     <row r="74" spans="1:18">
@@ -10290,43 +10294,43 @@
         <v>0</v>
       </c>
       <c r="F74" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="G74" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="H74" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="I74" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="J74" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="K74" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="L74" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="M74" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="N74" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="O74" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="P74" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="Q74" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="R74" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
     </row>
     <row r="75" spans="1:18">
@@ -10344,43 +10348,43 @@
         <v>0</v>
       </c>
       <c r="F75" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="G75" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="H75" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="I75" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="J75" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="K75" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="L75" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="M75" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="N75" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="O75" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="P75" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="Q75" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="R75" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
     </row>
     <row r="76" spans="1:18">
@@ -10452,43 +10456,43 @@
         <v>4095441.930000001</v>
       </c>
       <c r="F77" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="G77" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="H77" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="I77" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="J77" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="K77" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="L77" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="M77" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="N77" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="O77" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="P77" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="Q77" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="R77" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
     </row>
     <row r="78" spans="1:18">
@@ -10506,43 +10510,43 @@
         <v>0</v>
       </c>
       <c r="F78" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="G78" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="H78" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="I78" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="J78" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="K78" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="L78" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="M78" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="N78" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="O78" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="P78" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="Q78" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="R78" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
     </row>
     <row r="79" spans="1:18">
@@ -10560,43 +10564,43 @@
         <v>0</v>
       </c>
       <c r="F79" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="G79" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="H79" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="I79" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="J79" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="K79" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="L79" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="M79" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="N79" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="O79" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="P79" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="Q79" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="R79" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
     </row>
     <row r="80" spans="1:18">
@@ -10668,43 +10672,43 @@
         <v>0</v>
       </c>
       <c r="F81" s="3">
-        <v>7316921.561150696</v>
+        <v>7321575.790986921</v>
       </c>
       <c r="G81" s="3">
-        <v>7316921.561150696</v>
+        <v>7321575.790986921</v>
       </c>
       <c r="H81" s="3">
-        <v>7316921.561150696</v>
+        <v>7321575.790986921</v>
       </c>
       <c r="I81" s="3">
-        <v>7316921.561150696</v>
+        <v>7321575.790986921</v>
       </c>
       <c r="J81" s="3">
-        <v>7316921.561150696</v>
+        <v>7321575.790986921</v>
       </c>
       <c r="K81" s="3">
-        <v>7316921.561150696</v>
+        <v>7321575.790986921</v>
       </c>
       <c r="L81" s="3">
-        <v>7316921.561150696</v>
+        <v>7321575.790986921</v>
       </c>
       <c r="M81" s="3">
-        <v>7316921.561150696</v>
+        <v>7321575.790986921</v>
       </c>
       <c r="N81" s="3">
-        <v>7316921.561150696</v>
+        <v>7321575.790986921</v>
       </c>
       <c r="O81" s="3">
-        <v>7316921.561150696</v>
+        <v>7321575.790986921</v>
       </c>
       <c r="P81" s="3">
-        <v>7316921.561150696</v>
+        <v>7321575.790986921</v>
       </c>
       <c r="Q81" s="3">
-        <v>7316921.561150696</v>
+        <v>7321575.790986921</v>
       </c>
       <c r="R81" s="3">
-        <v>7316921.561150696</v>
+        <v>7321575.790986921</v>
       </c>
     </row>
     <row r="82" spans="1:18">
@@ -10722,43 +10726,43 @@
         <v>0</v>
       </c>
       <c r="F82" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="G82" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="H82" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="I82" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="J82" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="K82" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="L82" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="M82" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="N82" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="O82" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="P82" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="Q82" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
       <c r="R82" s="3">
-        <v>208504.2517704759</v>
+        <v>207922.4730409479</v>
       </c>
     </row>
     <row r="83" spans="1:18">
@@ -10942,4 +10946,1420 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:R28"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:18">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+      <c r="N1" s="1">
+        <v>2027</v>
+      </c>
+      <c r="O1" s="1">
+        <v>2028</v>
+      </c>
+      <c r="P1" s="1">
+        <v>2029</v>
+      </c>
+      <c r="Q1" s="1">
+        <v>2030</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
+      <c r="A2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3">
+        <v>22211081209.352</v>
+      </c>
+      <c r="F2" s="3">
+        <v>22491200730.71933</v>
+      </c>
+      <c r="G2" s="3">
+        <v>22841453115.40232</v>
+      </c>
+      <c r="H2" s="3">
+        <v>23220132817.26761</v>
+      </c>
+      <c r="I2" s="3">
+        <v>23671982667.74072</v>
+      </c>
+      <c r="J2" s="3">
+        <v>24155580257.38241</v>
+      </c>
+      <c r="K2" s="3">
+        <v>24600947254.14337</v>
+      </c>
+      <c r="L2" s="3">
+        <v>25162141405.84291</v>
+      </c>
+      <c r="M2" s="3">
+        <v>25695456299.79787</v>
+      </c>
+      <c r="N2" s="3">
+        <v>26236433233.89094</v>
+      </c>
+      <c r="O2" s="3">
+        <v>26776254404.08141</v>
+      </c>
+      <c r="P2" s="3">
+        <v>27380249493.03607</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>27943313961.31306</v>
+      </c>
+      <c r="R2" s="3">
+        <v>322386226849.97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
+      <c r="A3" s="2"/>
+      <c r="B3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3">
+        <v>57597434306.92513</v>
+      </c>
+      <c r="F3" s="3">
+        <v>57869096448.73486</v>
+      </c>
+      <c r="G3" s="3">
+        <v>58167418603.63599</v>
+      </c>
+      <c r="H3" s="3">
+        <v>58540311271.66576</v>
+      </c>
+      <c r="I3" s="3">
+        <v>59068822075.11604</v>
+      </c>
+      <c r="J3" s="3">
+        <v>59767624971.22166</v>
+      </c>
+      <c r="K3" s="3">
+        <v>60635538208.19434</v>
+      </c>
+      <c r="L3" s="3">
+        <v>61636522328.47</v>
+      </c>
+      <c r="M3" s="3">
+        <v>62741679927.37234</v>
+      </c>
+      <c r="N3" s="3">
+        <v>63952909880.60461</v>
+      </c>
+      <c r="O3" s="3">
+        <v>65242255754.8438</v>
+      </c>
+      <c r="P3" s="3">
+        <v>66581998500.42602</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>67969243805.25626</v>
+      </c>
+      <c r="R3" s="3">
+        <v>799770856082.4667</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
+      <c r="A4" s="2"/>
+      <c r="B4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3">
+        <v>537662353.0209763</v>
+      </c>
+      <c r="F4" s="3">
+        <v>540069789.7341413</v>
+      </c>
+      <c r="G4" s="3">
+        <v>544676524.8809783</v>
+      </c>
+      <c r="H4" s="3">
+        <v>550914126.590134</v>
+      </c>
+      <c r="I4" s="3">
+        <v>558750273.8255361</v>
+      </c>
+      <c r="J4" s="3">
+        <v>568002431.3921026</v>
+      </c>
+      <c r="K4" s="3">
+        <v>577858693.640415</v>
+      </c>
+      <c r="L4" s="3">
+        <v>588734317.7669237</v>
+      </c>
+      <c r="M4" s="3">
+        <v>600424742.9289706</v>
+      </c>
+      <c r="N4" s="3">
+        <v>612474709.7211798</v>
+      </c>
+      <c r="O4" s="3">
+        <v>624753377.7707846</v>
+      </c>
+      <c r="P4" s="3">
+        <v>637625543.2008628</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>650762286.3030888</v>
+      </c>
+      <c r="R4" s="3">
+        <v>7592709170.776094</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="A5" s="2"/>
+      <c r="B5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>376542417.3554893</v>
+      </c>
+      <c r="F5" s="3">
+        <v>383476364.7509683</v>
+      </c>
+      <c r="G5" s="3">
+        <v>390480377.3228644</v>
+      </c>
+      <c r="H5" s="3">
+        <v>397431460.3602202</v>
+      </c>
+      <c r="I5" s="3">
+        <v>405963880.9287609</v>
+      </c>
+      <c r="J5" s="3">
+        <v>414653141.1568951</v>
+      </c>
+      <c r="K5" s="3">
+        <v>421768495.4736052</v>
+      </c>
+      <c r="L5" s="3">
+        <v>431882965.6867499</v>
+      </c>
+      <c r="M5" s="3">
+        <v>440728656.7008117</v>
+      </c>
+      <c r="N5" s="3">
+        <v>449426276.2505687</v>
+      </c>
+      <c r="O5" s="3">
+        <v>458119921.2140281</v>
+      </c>
+      <c r="P5" s="3">
+        <v>468390664.9565358</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>477240732.8306935</v>
+      </c>
+      <c r="R5" s="3">
+        <v>5516105354.988191</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="A6" s="2"/>
+      <c r="B6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
+        <v>257028461.5827101</v>
+      </c>
+      <c r="F6" s="3">
+        <v>264430340.7629785</v>
+      </c>
+      <c r="G6" s="3">
+        <v>270952690.5897198</v>
+      </c>
+      <c r="H6" s="3">
+        <v>277120234.6731567</v>
+      </c>
+      <c r="I6" s="3">
+        <v>284513764.8893429</v>
+      </c>
+      <c r="J6" s="3">
+        <v>292240424.2939516</v>
+      </c>
+      <c r="K6" s="3">
+        <v>298725180.5304567</v>
+      </c>
+      <c r="L6" s="3">
+        <v>307367615.3532559</v>
+      </c>
+      <c r="M6" s="3">
+        <v>315398626.6400128</v>
+      </c>
+      <c r="N6" s="3">
+        <v>323107796.9987953</v>
+      </c>
+      <c r="O6" s="3">
+        <v>330821083.4427713</v>
+      </c>
+      <c r="P6" s="3">
+        <v>339796293.7580515</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>347791073.8096377</v>
+      </c>
+      <c r="R6" s="3">
+        <v>3909293587.324841</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
+      <c r="A7" s="2"/>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>498532403.3582104</v>
+      </c>
+      <c r="F7" s="3">
+        <v>508315045.0125645</v>
+      </c>
+      <c r="G7" s="3">
+        <v>520543347.0805075</v>
+      </c>
+      <c r="H7" s="3">
+        <v>530325988.7348616</v>
+      </c>
+      <c r="I7" s="3">
+        <v>540108630.3892156</v>
+      </c>
+      <c r="J7" s="3">
+        <v>552336932.4571584</v>
+      </c>
+      <c r="K7" s="3">
+        <v>564565234.5251011</v>
+      </c>
+      <c r="L7" s="3">
+        <v>574347876.1794554</v>
+      </c>
+      <c r="M7" s="3">
+        <v>589021838.6609868</v>
+      </c>
+      <c r="N7" s="3">
+        <v>601250140.7289292</v>
+      </c>
+      <c r="O7" s="3">
+        <v>613478442.7968723</v>
+      </c>
+      <c r="P7" s="3">
+        <v>625706744.864815</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>640380707.3463464</v>
+      </c>
+      <c r="R7" s="3">
+        <v>7358913332.135025</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="A8" s="2"/>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>85060.00982304836</v>
+      </c>
+      <c r="F8" s="3">
+        <v>87377.7511833305</v>
+      </c>
+      <c r="G8" s="3">
+        <v>89380.97604674904</v>
+      </c>
+      <c r="H8" s="3">
+        <v>91301.05527788764</v>
+      </c>
+      <c r="I8" s="3">
+        <v>93622.74944426618</v>
+      </c>
+      <c r="J8" s="3">
+        <v>96023.98210304328</v>
+      </c>
+      <c r="K8" s="3">
+        <v>98019.82798761656</v>
+      </c>
+      <c r="L8" s="3">
+        <v>100751.5994268555</v>
+      </c>
+      <c r="M8" s="3">
+        <v>103225.6868523028</v>
+      </c>
+      <c r="N8" s="3">
+        <v>105625.6563460976</v>
+      </c>
+      <c r="O8" s="3">
+        <v>108025.3554714074</v>
+      </c>
+      <c r="P8" s="3">
+        <v>110836.8324829971</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>113303.816146075</v>
+      </c>
+      <c r="R8" s="3">
+        <v>1282555.298591677</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="A9" s="2"/>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
+        <v>81101823794.24886</v>
+      </c>
+      <c r="F9" s="3">
+        <v>81673199732.71507</v>
+      </c>
+      <c r="G9" s="3">
+        <v>82345133662.56555</v>
+      </c>
+      <c r="H9" s="3">
+        <v>83118895739.9868</v>
+      </c>
+      <c r="I9" s="3">
+        <v>84124271034.7103</v>
+      </c>
+      <c r="J9" s="3">
+        <v>85335881040.72937</v>
+      </c>
+      <c r="K9" s="3">
+        <v>86677732590.86166</v>
+      </c>
+      <c r="L9" s="3">
+        <v>88269214295.21198</v>
+      </c>
+      <c r="M9" s="3">
+        <v>89942084661.08704</v>
+      </c>
+      <c r="N9" s="3">
+        <v>91726281387.6008</v>
+      </c>
+      <c r="O9" s="3">
+        <v>93587671088.29109</v>
+      </c>
+      <c r="P9" s="3">
+        <v>95565487412.11833</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>97551605137.84453</v>
+      </c>
+      <c r="R9" s="3">
+        <v>1141019281577.971</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="A10" s="2"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="A11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
+        <v>22174873774.08001</v>
+      </c>
+      <c r="F11" s="3">
+        <v>21108647027.04025</v>
+      </c>
+      <c r="G11" s="3">
+        <v>21460920501.88671</v>
+      </c>
+      <c r="H11" s="3">
+        <v>21847370250.51009</v>
+      </c>
+      <c r="I11" s="3">
+        <v>22295391671.88422</v>
+      </c>
+      <c r="J11" s="3">
+        <v>22774849256.37924</v>
+      </c>
+      <c r="K11" s="3">
+        <v>23226964484.65923</v>
+      </c>
+      <c r="L11" s="3">
+        <v>23785028770.53642</v>
+      </c>
+      <c r="M11" s="3">
+        <v>24313709973.40934</v>
+      </c>
+      <c r="N11" s="3">
+        <v>24861422440.36335</v>
+      </c>
+      <c r="O11" s="3">
+        <v>25402309449.66431</v>
+      </c>
+      <c r="P11" s="3">
+        <v>26002720088.03078</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>26566391470.76495</v>
+      </c>
+      <c r="R11" s="3">
+        <v>305820599159.2089</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="A12" s="2"/>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
+        <v>57492330656.34814</v>
+      </c>
+      <c r="F12" s="3">
+        <v>57641971952.32352</v>
+      </c>
+      <c r="G12" s="3">
+        <v>57735670638.70547</v>
+      </c>
+      <c r="H12" s="3">
+        <v>57924562177.52044</v>
+      </c>
+      <c r="I12" s="3">
+        <v>58315193542.85978</v>
+      </c>
+      <c r="J12" s="3">
+        <v>58914832028.52785</v>
+      </c>
+      <c r="K12" s="3">
+        <v>59712102767.84681</v>
+      </c>
+      <c r="L12" s="3">
+        <v>60663218356.80781</v>
+      </c>
+      <c r="M12" s="3">
+        <v>61733040052.31509</v>
+      </c>
+      <c r="N12" s="3">
+        <v>62919048637.51784</v>
+      </c>
+      <c r="O12" s="3">
+        <v>64190694874.63803</v>
+      </c>
+      <c r="P12" s="3">
+        <v>65517949178.68291</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>66896194211.40559</v>
+      </c>
+      <c r="R12" s="3">
+        <v>789656809075.4993</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="A13" s="2"/>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3">
+        <v>554491654.1201342</v>
+      </c>
+      <c r="F13" s="3">
+        <v>557506957.5949601</v>
+      </c>
+      <c r="G13" s="3">
+        <v>562923875.9578997</v>
+      </c>
+      <c r="H13" s="3">
+        <v>569776230.3191302</v>
+      </c>
+      <c r="I13" s="3">
+        <v>578069470.0988536</v>
+      </c>
+      <c r="J13" s="3">
+        <v>587661883.5021286</v>
+      </c>
+      <c r="K13" s="3">
+        <v>597748254.4252005</v>
+      </c>
+      <c r="L13" s="3">
+        <v>608798108.2711726</v>
+      </c>
+      <c r="M13" s="3">
+        <v>620620842.7288345</v>
+      </c>
+      <c r="N13" s="3">
+        <v>632754362.387319</v>
+      </c>
+      <c r="O13" s="3">
+        <v>645086550.932328</v>
+      </c>
+      <c r="P13" s="3">
+        <v>658005665.2691336</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>671173276.0369809</v>
+      </c>
+      <c r="R13" s="3">
+        <v>7844617131.644075</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
+      <c r="A14" s="2"/>
+      <c r="B14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>376645921.5124688</v>
+      </c>
+      <c r="F14" s="3">
+        <v>385319196.1141558</v>
+      </c>
+      <c r="G14" s="3">
+        <v>392476680.5183489</v>
+      </c>
+      <c r="H14" s="3">
+        <v>399429140.4191912</v>
+      </c>
+      <c r="I14" s="3">
+        <v>407968100.7111775</v>
+      </c>
+      <c r="J14" s="3">
+        <v>416664188.717358</v>
+      </c>
+      <c r="K14" s="3">
+        <v>423771188.1913379</v>
+      </c>
+      <c r="L14" s="3">
+        <v>433890882.7379955</v>
+      </c>
+      <c r="M14" s="3">
+        <v>442742709.0594019</v>
+      </c>
+      <c r="N14" s="3">
+        <v>451432223.2668582</v>
+      </c>
+      <c r="O14" s="3">
+        <v>460123749.1825457</v>
+      </c>
+      <c r="P14" s="3">
+        <v>470399673.4268938</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>479248707.0213733</v>
+      </c>
+      <c r="R14" s="3">
+        <v>5540112360.879107</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="A15" s="2"/>
+      <c r="B15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>170932913.276664</v>
+      </c>
+      <c r="F15" s="3">
+        <v>178957564.6528735</v>
+      </c>
+      <c r="G15" s="3">
+        <v>185935922.9328065</v>
+      </c>
+      <c r="H15" s="3">
+        <v>192150357.6025435</v>
+      </c>
+      <c r="I15" s="3">
+        <v>199225738.3250566</v>
+      </c>
+      <c r="J15" s="3">
+        <v>207020814.819009</v>
+      </c>
+      <c r="K15" s="3">
+        <v>213918744.9569666</v>
+      </c>
+      <c r="L15" s="3">
+        <v>221911441.3952305</v>
+      </c>
+      <c r="M15" s="3">
+        <v>230362578.9266288</v>
+      </c>
+      <c r="N15" s="3">
+        <v>238124010.9236651</v>
+      </c>
+      <c r="O15" s="3">
+        <v>245890451.9030555</v>
+      </c>
+      <c r="P15" s="3">
+        <v>254600050.3068004</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>262973476.1246122</v>
+      </c>
+      <c r="R15" s="3">
+        <v>2802004066.145912</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="A16" s="2"/>
+      <c r="B16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3">
+        <v>478394303.7450669</v>
+      </c>
+      <c r="F16" s="3">
+        <v>488176945.3994209</v>
+      </c>
+      <c r="G16" s="3">
+        <v>500405247.4673638</v>
+      </c>
+      <c r="H16" s="3">
+        <v>510187889.1217179</v>
+      </c>
+      <c r="I16" s="3">
+        <v>519970530.7760721</v>
+      </c>
+      <c r="J16" s="3">
+        <v>532198832.8440149</v>
+      </c>
+      <c r="K16" s="3">
+        <v>544427134.9119576</v>
+      </c>
+      <c r="L16" s="3">
+        <v>554209776.5663116</v>
+      </c>
+      <c r="M16" s="3">
+        <v>568883739.0478432</v>
+      </c>
+      <c r="N16" s="3">
+        <v>581112041.1157856</v>
+      </c>
+      <c r="O16" s="3">
+        <v>593340343.1837287</v>
+      </c>
+      <c r="P16" s="3">
+        <v>605568645.2516714</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>620242607.7332029</v>
+      </c>
+      <c r="R16" s="3">
+        <v>7097118037.164158</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
+      <c r="A17" s="2"/>
+      <c r="B17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
+        <v>64534.39529364954</v>
+      </c>
+      <c r="F17" s="3">
+        <v>66765.54942119546</v>
+      </c>
+      <c r="G17" s="3">
+        <v>68870.98354955023</v>
+      </c>
+      <c r="H17" s="3">
+        <v>70797.60295686778</v>
+      </c>
+      <c r="I17" s="3">
+        <v>73037.25807117697</v>
+      </c>
+      <c r="J17" s="3">
+        <v>75447.97031669036</v>
+      </c>
+      <c r="K17" s="3">
+        <v>77537.53506011683</v>
+      </c>
+      <c r="L17" s="3">
+        <v>80108.4251601943</v>
+      </c>
+      <c r="M17" s="3">
+        <v>82675.82037775483</v>
+      </c>
+      <c r="N17" s="3">
+        <v>85083.81603446216</v>
+      </c>
+      <c r="O17" s="3">
+        <v>87491.23023109864</v>
+      </c>
+      <c r="P17" s="3">
+        <v>90233.53678799063</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>92785.65450688318</v>
+      </c>
+      <c r="R17" s="3">
+        <v>1015369.777767631</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
+      <c r="A18" s="2"/>
+      <c r="B18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3">
+        <v>80871087835.96532</v>
+      </c>
+      <c r="F18" s="3">
+        <v>79975327212.56044</v>
+      </c>
+      <c r="G18" s="3">
+        <v>80445925057.93379</v>
+      </c>
+      <c r="H18" s="3">
+        <v>81044117702.67688</v>
+      </c>
+      <c r="I18" s="3">
+        <v>81907923991.20206</v>
+      </c>
+      <c r="J18" s="3">
+        <v>83016638264.04256</v>
+      </c>
+      <c r="K18" s="3">
+        <v>84295238924.33524</v>
+      </c>
+      <c r="L18" s="3">
+        <v>85833246562.00211</v>
+      </c>
+      <c r="M18" s="3">
+        <v>87466699862.24811</v>
+      </c>
+      <c r="N18" s="3">
+        <v>89232546576.12399</v>
+      </c>
+      <c r="O18" s="3">
+        <v>91077409161.55168</v>
+      </c>
+      <c r="P18" s="3">
+        <v>93038933861.07808</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>95017067827.71985</v>
+      </c>
+      <c r="R18" s="3">
+        <v>1113222162839.44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
+      <c r="A19" s="2"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="1:18">
+      <c r="A20" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>22116253715.66332</v>
+      </c>
+      <c r="F20" s="3">
+        <v>20420994645.79013</v>
+      </c>
+      <c r="G20" s="3">
+        <v>20771509649.63514</v>
+      </c>
+      <c r="H20" s="3">
+        <v>21159655108.05441</v>
+      </c>
+      <c r="I20" s="3">
+        <v>21604467435.44141</v>
+      </c>
+      <c r="J20" s="3">
+        <v>22080886163.10287</v>
+      </c>
+      <c r="K20" s="3">
+        <v>22535257964.70835</v>
+      </c>
+      <c r="L20" s="3">
+        <v>23091150210.64363</v>
+      </c>
+      <c r="M20" s="3">
+        <v>23617066601.45523</v>
+      </c>
+      <c r="N20" s="3">
+        <v>24167392955.56987</v>
+      </c>
+      <c r="O20" s="3">
+        <v>24708333086.26275</v>
+      </c>
+      <c r="P20" s="3">
+        <v>25306682647.37967</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>25870278572.07784</v>
+      </c>
+      <c r="R20" s="3">
+        <v>297449928755.7846</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
+      <c r="A21" s="2"/>
+      <c r="B21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
+        <v>56710984810.87008</v>
+      </c>
+      <c r="F21" s="3">
+        <v>56650690319.25446</v>
+      </c>
+      <c r="G21" s="3">
+        <v>56536713572.00832</v>
+      </c>
+      <c r="H21" s="3">
+        <v>56559649854.79473</v>
+      </c>
+      <c r="I21" s="3">
+        <v>56827201462.59061</v>
+      </c>
+      <c r="J21" s="3">
+        <v>57336890657.5496</v>
+      </c>
+      <c r="K21" s="3">
+        <v>58068135644.8448</v>
+      </c>
+      <c r="L21" s="3">
+        <v>58970374118.81216</v>
+      </c>
+      <c r="M21" s="3">
+        <v>60003884151.02452</v>
+      </c>
+      <c r="N21" s="3">
+        <v>61162302070.12635</v>
+      </c>
+      <c r="O21" s="3">
+        <v>62412740549.30882</v>
+      </c>
+      <c r="P21" s="3">
+        <v>63723523361.52563</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>65088805475.06082</v>
+      </c>
+      <c r="R21" s="3">
+        <v>770051896047.7709</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
+      <c r="A22" s="2"/>
+      <c r="B22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>553608983.4906435</v>
+      </c>
+      <c r="F22" s="3">
+        <v>556934243.9927058</v>
+      </c>
+      <c r="G22" s="3">
+        <v>562704681.9292293</v>
+      </c>
+      <c r="H22" s="3">
+        <v>569821086.080349</v>
+      </c>
+      <c r="I22" s="3">
+        <v>578303685.2751822</v>
+      </c>
+      <c r="J22" s="3">
+        <v>588032459.8571357</v>
+      </c>
+      <c r="K22" s="3">
+        <v>598216323.9351237</v>
+      </c>
+      <c r="L22" s="3">
+        <v>609335307.9490631</v>
+      </c>
+      <c r="M22" s="3">
+        <v>621208755.0826558</v>
+      </c>
+      <c r="N22" s="3">
+        <v>633378303.1733822</v>
+      </c>
+      <c r="O22" s="3">
+        <v>645735737.1091161</v>
+      </c>
+      <c r="P22" s="3">
+        <v>658673101.9670923</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>671854416.1225097</v>
+      </c>
+      <c r="R22" s="3">
+        <v>7847807085.964189</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
+      <c r="A23" s="2"/>
+      <c r="B23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="3">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3">
+        <v>378064447.8423566</v>
+      </c>
+      <c r="F23" s="3">
+        <v>387578541.0656824</v>
+      </c>
+      <c r="G23" s="3">
+        <v>394818208.2182666</v>
+      </c>
+      <c r="H23" s="3">
+        <v>401773712.1109512</v>
+      </c>
+      <c r="I23" s="3">
+        <v>410321325.5408045</v>
+      </c>
+      <c r="J23" s="3">
+        <v>419023003.4331913</v>
+      </c>
+      <c r="K23" s="3">
+        <v>426121152.7531943</v>
+      </c>
+      <c r="L23" s="3">
+        <v>436250163.6277329</v>
+      </c>
+      <c r="M23" s="3">
+        <v>445103504.5253589</v>
+      </c>
+      <c r="N23" s="3">
+        <v>453787240.3567241</v>
+      </c>
+      <c r="O23" s="3">
+        <v>462476388.2690597</v>
+      </c>
+      <c r="P23" s="3">
+        <v>472758348.8194222</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>481603820.9517874</v>
+      </c>
+      <c r="R23" s="3">
+        <v>5569679857.514531</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
+      <c r="A24" s="2"/>
+      <c r="B24" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>130937881.6388058</v>
+      </c>
+      <c r="F24" s="3">
+        <v>138925964.8114338</v>
+      </c>
+      <c r="G24" s="3">
+        <v>146123806.9200122</v>
+      </c>
+      <c r="H24" s="3">
+        <v>152367355.7800044</v>
+      </c>
+      <c r="I24" s="3">
+        <v>159299272.4850093</v>
+      </c>
+      <c r="J24" s="3">
+        <v>167131648.597439</v>
+      </c>
+      <c r="K24" s="3">
+        <v>174229317.4913088</v>
+      </c>
+      <c r="L24" s="3">
+        <v>181924088.5469114</v>
+      </c>
+      <c r="M24" s="3">
+        <v>190576461.1673259</v>
+      </c>
+      <c r="N24" s="3">
+        <v>198369132.1539893</v>
+      </c>
+      <c r="O24" s="3">
+        <v>206165828.021296</v>
+      </c>
+      <c r="P24" s="3">
+        <v>214756391.090572</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>223311858.243183</v>
+      </c>
+      <c r="R24" s="3">
+        <v>2284119006.947291</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
+      <c r="A25" s="2"/>
+      <c r="B25" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" s="3">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3">
+        <v>469039302.8536044</v>
+      </c>
+      <c r="F25" s="3">
+        <v>478821944.5079585</v>
+      </c>
+      <c r="G25" s="3">
+        <v>491050246.5759012</v>
+      </c>
+      <c r="H25" s="3">
+        <v>500832888.2302553</v>
+      </c>
+      <c r="I25" s="3">
+        <v>510615529.8846096</v>
+      </c>
+      <c r="J25" s="3">
+        <v>522843831.9525523</v>
+      </c>
+      <c r="K25" s="3">
+        <v>535072134.020495</v>
+      </c>
+      <c r="L25" s="3">
+        <v>544854775.6748492</v>
+      </c>
+      <c r="M25" s="3">
+        <v>559528738.1563804</v>
+      </c>
+      <c r="N25" s="3">
+        <v>571757040.2243232</v>
+      </c>
+      <c r="O25" s="3">
+        <v>583985342.292266</v>
+      </c>
+      <c r="P25" s="3">
+        <v>596213644.3602089</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>610887606.8417399</v>
+      </c>
+      <c r="R25" s="3">
+        <v>6975503025.575143</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
+      <c r="A26" s="2"/>
+      <c r="B26" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="3">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3">
+        <v>54999.37729746195</v>
+      </c>
+      <c r="F26" s="3">
+        <v>57190.30798511048</v>
+      </c>
+      <c r="G26" s="3">
+        <v>59343.22264951193</v>
+      </c>
+      <c r="H26" s="3">
+        <v>61272.88024589198</v>
+      </c>
+      <c r="I26" s="3">
+        <v>63474.42474301355</v>
+      </c>
+      <c r="J26" s="3">
+        <v>65889.54065839013</v>
+      </c>
+      <c r="K26" s="3">
+        <v>68022.64178434327</v>
+      </c>
+      <c r="L26" s="3">
+        <v>70518.79568288301</v>
+      </c>
+      <c r="M26" s="3">
+        <v>73129.53632504508</v>
+      </c>
+      <c r="N26" s="3">
+        <v>75541.26047464115</v>
+      </c>
+      <c r="O26" s="3">
+        <v>77952.25864893814</v>
+      </c>
+      <c r="P26" s="3">
+        <v>80662.43259760037</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>83254.09869411246</v>
+      </c>
+      <c r="R26" s="3">
+        <v>891250.7777869436</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
+      <c r="A27" s="2"/>
+      <c r="B27" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27" s="3">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3">
+        <v>79980879693.89377</v>
+      </c>
+      <c r="F27" s="3">
+        <v>78246424308.66469</v>
+      </c>
+      <c r="G27" s="3">
+        <v>78508161300.29126</v>
+      </c>
+      <c r="H27" s="3">
+        <v>78942387565.82001</v>
+      </c>
+      <c r="I27" s="3">
+        <v>79679950860.10156</v>
+      </c>
+      <c r="J27" s="3">
+        <v>80695850650.60025</v>
+      </c>
+      <c r="K27" s="3">
+        <v>81910979407.64185</v>
+      </c>
+      <c r="L27" s="3">
+        <v>83397709020.42229</v>
+      </c>
+      <c r="M27" s="3">
+        <v>84992337836.42245</v>
+      </c>
+      <c r="N27" s="3">
+        <v>86733275042.50839</v>
+      </c>
+      <c r="O27" s="3">
+        <v>88557038495.2529</v>
+      </c>
+      <c r="P27" s="3">
+        <v>90499929808.75578</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>92465221182.44478</v>
+      </c>
+      <c r="R27" s="3">
+        <v>1084610145172.82</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
+      <c r="A28" s="2"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>